--- a/dptest/Templates/Report Templates/Memphis templates/JAWHA/OQC_Report_Memphis_MP_Y_Carrier_.xlsx
+++ b/dptest/Templates/Report Templates/Memphis templates/JAWHA/OQC_Report_Memphis_MP_Y_Carrier_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user01\Desktop\Memphis templates (2)\Memphis templates\JAWHA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\JTMES\Templates\Report Templates\Memphis templates\JAWHA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAE8B8B-3036-4D47-BE15-D0FD5CA710EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF716392-D495-4C2D-9612-6D26B625B968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="816" xr2:uid="{558B7DC1-779D-BB42-B43A-ED7A08375808}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" tabRatio="816" xr2:uid="{558B7DC1-779D-BB42-B43A-ED7A08375808}"/>
   </bookViews>
   <sheets>
     <sheet name="Waiver Summary" sheetId="5" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="FAI" sheetId="21" r:id="rId3"/>
     <sheet name="SPC" sheetId="22" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <definedNames>
     <definedName name="________XG2" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="________XG2" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
@@ -2264,7 +2261,7 @@
     <definedName name="ㅂㅂ" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅂㅂ" localSheetId="2" hidden="1">FAI!ㅂㅂㅂ</definedName>
     <definedName name="ㅂㅂㅂ" localSheetId="3" hidden="1">SPC!ㅂㅂㅂ</definedName>
-    <definedName name="ㅂㅂㅂ" hidden="1">[1]!ㅂㅂㅂ</definedName>
+    <definedName name="ㅂㅂㅂ" hidden="1">#REF!</definedName>
     <definedName name="ㅂㅈㅇㅇ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅈㅇㅇ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
     <definedName name="ㅂㅈㅇㅇ" hidden="1">{#N/A,#N/A,FALSE,"단축1";#N/A,#N/A,FALSE,"단축2";#N/A,#N/A,FALSE,"단축3";#N/A,#N/A,FALSE,"장축";#N/A,#N/A,FALSE,"4WD"}</definedName>
@@ -7760,87 +7757,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="39" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -7857,10 +7773,96 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="39" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="694">
     <cellStyle name="___CPK__" xfId="52" xr:uid="{66B5D527-70B2-400F-8B63-DFBD3372561C}"/>
-    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 2" xfId="29" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 3" xfId="33" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 4" xfId="37" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 5" xfId="41" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 6" xfId="45" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - 강조색1 10" xfId="226" xr:uid="{144ACF6C-EC76-4508-8082-1FFC5044376A}"/>
     <cellStyle name="20% - 강조색1 10 2" xfId="552" xr:uid="{E8F9FED5-EF02-4838-BCE1-BB17C9AE1CCF}"/>
     <cellStyle name="20% - 강조색1 11" xfId="246" xr:uid="{A0133E03-4FF6-4773-83EB-E1C71755515E}"/>
@@ -7892,7 +7894,6 @@
     <cellStyle name="20% - 강조색1 8 2" xfId="512" xr:uid="{B51293B8-7FFB-4DBA-BDD3-4C08AA726E70}"/>
     <cellStyle name="20% - 강조색1 9" xfId="206" xr:uid="{3AF2B297-8D3F-4630-89A2-074B4220D709}"/>
     <cellStyle name="20% - 강조색1 9 2" xfId="532" xr:uid="{7A8228DA-BD73-4843-953B-BE63140ED1CE}"/>
-    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 강조색2 10" xfId="229" xr:uid="{626F9513-4C92-4F94-B200-104CF2CD402B}"/>
     <cellStyle name="20% - 강조색2 10 2" xfId="555" xr:uid="{890507FD-E5FC-4FEA-A63A-E400DCD61AA3}"/>
     <cellStyle name="20% - 강조색2 11" xfId="249" xr:uid="{26249CFF-D7A2-4344-AF21-7004B903DE59}"/>
@@ -7924,7 +7925,6 @@
     <cellStyle name="20% - 강조색2 8 2" xfId="515" xr:uid="{1A70B3D7-1E9C-4AD2-8E38-97C6CABAF110}"/>
     <cellStyle name="20% - 강조색2 9" xfId="209" xr:uid="{87FEFB61-F2A8-431E-926D-D0AA74DBDF54}"/>
     <cellStyle name="20% - 강조색2 9 2" xfId="535" xr:uid="{94061066-09E5-41C2-9471-91DA84E608BD}"/>
-    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38" customBuiltin="1"/>
     <cellStyle name="20% - 강조색3 10" xfId="232" xr:uid="{61651A33-B832-41AE-9EBF-C4749E3E2278}"/>
     <cellStyle name="20% - 강조색3 10 2" xfId="558" xr:uid="{2676F700-AC82-4A42-934E-3075BB291FC5}"/>
     <cellStyle name="20% - 강조색3 11" xfId="252" xr:uid="{E949058E-E0C6-4200-8EC6-DBEF142DAD18}"/>
@@ -7956,7 +7956,6 @@
     <cellStyle name="20% - 강조색3 8 2" xfId="518" xr:uid="{12D2E9EF-C5A5-44B2-83C3-7DC5927E5710}"/>
     <cellStyle name="20% - 강조색3 9" xfId="212" xr:uid="{B05A3FC1-2BD3-4D5D-BBD1-AF122FFA97D0}"/>
     <cellStyle name="20% - 강조색3 9 2" xfId="538" xr:uid="{5A2BECAA-F255-40C3-8421-6A4601240941}"/>
-    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42" customBuiltin="1"/>
     <cellStyle name="20% - 강조색4 10" xfId="235" xr:uid="{D7777BE9-BACF-476F-AC89-842F95EB340A}"/>
     <cellStyle name="20% - 강조색4 10 2" xfId="561" xr:uid="{71967C4B-E571-4B8A-9563-A1FE564F08F1}"/>
     <cellStyle name="20% - 강조색4 11" xfId="255" xr:uid="{8CECB8CF-16A3-4C86-9941-19EB25997AC4}"/>
@@ -7988,7 +7987,6 @@
     <cellStyle name="20% - 강조색4 8 2" xfId="521" xr:uid="{A2179F81-96C8-4BA5-A813-3E1DB94B41B0}"/>
     <cellStyle name="20% - 강조색4 9" xfId="215" xr:uid="{14FB7DB9-C519-47BE-8EC1-AA255607A88C}"/>
     <cellStyle name="20% - 강조색4 9 2" xfId="541" xr:uid="{EED34536-61FA-4658-9B9F-2318A6269995}"/>
-    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46" customBuiltin="1"/>
     <cellStyle name="20% - 강조색5 10" xfId="238" xr:uid="{E411D9CE-490D-4DFD-94EE-328AACF8795E}"/>
     <cellStyle name="20% - 강조색5 10 2" xfId="564" xr:uid="{65A503CD-CDED-4957-97BF-209C9429B45C}"/>
     <cellStyle name="20% - 강조색5 11" xfId="258" xr:uid="{A182F85F-D434-4461-A92A-139E7B12C467}"/>
@@ -8020,7 +8018,6 @@
     <cellStyle name="20% - 강조색5 8 2" xfId="524" xr:uid="{D1EB53DD-D986-43C6-81AF-D36C9E6A0501}"/>
     <cellStyle name="20% - 강조색5 9" xfId="218" xr:uid="{772F6110-8CBC-401D-913D-DFF9BBD2E526}"/>
     <cellStyle name="20% - 강조색5 9 2" xfId="544" xr:uid="{F9BCC682-A3D4-4A37-A29C-E3EF86CA1344}"/>
-    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - 강조색6 10" xfId="241" xr:uid="{A9D7E7EF-A19E-4C1A-AB1C-96A3CDA2DCD8}"/>
     <cellStyle name="20% - 강조색6 10 2" xfId="567" xr:uid="{229F6D76-36E4-41F4-B9F8-916ED5ED0987}"/>
     <cellStyle name="20% - 강조색6 11" xfId="261" xr:uid="{8D2F71CB-6051-471E-94A7-4CAE37718795}"/>
@@ -8052,7 +8049,12 @@
     <cellStyle name="20% - 강조색6 8 2" xfId="527" xr:uid="{1567BED1-894B-47B9-9B7A-D2F7A9729458}"/>
     <cellStyle name="20% - 강조색6 9" xfId="221" xr:uid="{CE3D1595-0958-48A2-B9EE-416DA293B80D}"/>
     <cellStyle name="20% - 강조색6 9 2" xfId="547" xr:uid="{C54790E1-8D89-4CF8-99BA-779727EF99C8}"/>
-    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 2" xfId="30" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 3" xfId="34" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 4" xfId="38" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 5" xfId="42" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 6" xfId="46" builtinId="51" customBuiltin="1"/>
     <cellStyle name="40% - 강조색1 10" xfId="227" xr:uid="{E08ED7FC-FA6B-4FD9-A116-0BE127A8255A}"/>
     <cellStyle name="40% - 강조색1 10 2" xfId="553" xr:uid="{3B6EDD84-2B70-4C89-8602-BDCAB73EB691}"/>
     <cellStyle name="40% - 강조색1 11" xfId="247" xr:uid="{1995D369-4950-4911-8B5B-D6D1B63DABEC}"/>
@@ -8084,7 +8086,6 @@
     <cellStyle name="40% - 강조색1 8 2" xfId="513" xr:uid="{E6BDE4DC-21A8-4C38-AEB2-C6434EA29095}"/>
     <cellStyle name="40% - 강조색1 9" xfId="207" xr:uid="{3AE69E2A-7B92-4C93-BFD7-548085599299}"/>
     <cellStyle name="40% - 강조색1 9 2" xfId="533" xr:uid="{5AC288D9-A9F5-4823-AE64-7030C4EB4C72}"/>
-    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35" customBuiltin="1"/>
     <cellStyle name="40% - 강조색2 10" xfId="230" xr:uid="{382D258B-D946-495B-BB96-23BC5A2A4906}"/>
     <cellStyle name="40% - 강조색2 10 2" xfId="556" xr:uid="{B74A1249-E683-4FD1-8A6C-C38B48C4B4D9}"/>
     <cellStyle name="40% - 강조색2 11" xfId="250" xr:uid="{BCC6833B-7F37-4366-AB03-A4189D5D1A5C}"/>
@@ -8116,7 +8117,6 @@
     <cellStyle name="40% - 강조색2 8 2" xfId="516" xr:uid="{F410D1F7-7C58-4ACE-820D-8FDF8F5C939A}"/>
     <cellStyle name="40% - 강조색2 9" xfId="210" xr:uid="{132DE09A-2130-4280-B94F-352BF1679BB9}"/>
     <cellStyle name="40% - 강조색2 9 2" xfId="536" xr:uid="{44CF8CF0-AE2D-4766-A8D9-869580757FDA}"/>
-    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39" customBuiltin="1"/>
     <cellStyle name="40% - 강조색3 10" xfId="233" xr:uid="{5DCA0145-145D-477F-9C69-0E7D0BDAA8CE}"/>
     <cellStyle name="40% - 강조색3 10 2" xfId="559" xr:uid="{826201E5-0736-4BF2-9DDC-FA9CBEE387D4}"/>
     <cellStyle name="40% - 강조색3 11" xfId="253" xr:uid="{12DE31AC-58EA-478B-B2F8-EC3A4EF8B964}"/>
@@ -8148,7 +8148,6 @@
     <cellStyle name="40% - 강조색3 8 2" xfId="519" xr:uid="{A9C3DDB0-8FEA-4009-A75E-3C7FDC17395B}"/>
     <cellStyle name="40% - 강조색3 9" xfId="213" xr:uid="{4A23610B-77CE-47A2-B2FB-E8C44A920724}"/>
     <cellStyle name="40% - 강조색3 9 2" xfId="539" xr:uid="{62F8445B-5FC7-4AAE-9BF1-492B7CBD76E7}"/>
-    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43" customBuiltin="1"/>
     <cellStyle name="40% - 강조색4 10" xfId="236" xr:uid="{279AACC2-5F8A-4635-BD30-C38CC99F5BBF}"/>
     <cellStyle name="40% - 강조색4 10 2" xfId="562" xr:uid="{D904CBF3-AD96-4BB6-B5BA-A376555F62A5}"/>
     <cellStyle name="40% - 강조색4 11" xfId="256" xr:uid="{9192174F-5DD8-40D2-8FBE-748F54596A66}"/>
@@ -8180,7 +8179,6 @@
     <cellStyle name="40% - 강조색4 8 2" xfId="522" xr:uid="{90EFC29F-E633-4F15-A6EA-BD8C6438F6C8}"/>
     <cellStyle name="40% - 강조색4 9" xfId="216" xr:uid="{5FE4A7DD-4F23-4F4B-9A91-26CA02F74E9F}"/>
     <cellStyle name="40% - 강조색4 9 2" xfId="542" xr:uid="{6E0F506F-D7E0-44F1-AC96-1A5A4F3830E8}"/>
-    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47" customBuiltin="1"/>
     <cellStyle name="40% - 강조색5 10" xfId="239" xr:uid="{BA76548E-7B5B-498D-8406-8634949E5754}"/>
     <cellStyle name="40% - 강조색5 10 2" xfId="565" xr:uid="{AAE5E940-EFED-434F-9788-ACB3835964F0}"/>
     <cellStyle name="40% - 강조색5 11" xfId="259" xr:uid="{424F185F-7460-4E6C-A653-EFCCE0B5C804}"/>
@@ -8212,7 +8210,6 @@
     <cellStyle name="40% - 강조색5 8 2" xfId="525" xr:uid="{C72E6ADE-7654-4BB8-A4D4-AA2048319308}"/>
     <cellStyle name="40% - 강조색5 9" xfId="219" xr:uid="{C3599F2D-029D-43AC-A322-099F96CB9902}"/>
     <cellStyle name="40% - 강조색5 9 2" xfId="545" xr:uid="{A0DDE44A-6DFD-4647-AB0F-467B3A4B6251}"/>
-    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51" customBuiltin="1"/>
     <cellStyle name="40% - 강조색6 10" xfId="242" xr:uid="{E82BFB48-84FD-41B7-AB7F-3FC7DAD9B6DF}"/>
     <cellStyle name="40% - 강조색6 10 2" xfId="568" xr:uid="{BA77E0A3-5094-4F23-BA11-86477752FD24}"/>
     <cellStyle name="40% - 강조색6 11" xfId="262" xr:uid="{7F222311-21F8-4F52-86D3-B6BCB9F92164}"/>
@@ -8244,7 +8241,12 @@
     <cellStyle name="40% - 강조색6 8 2" xfId="528" xr:uid="{D896379B-EDA5-4D41-8F54-E7EA47C0AEE4}"/>
     <cellStyle name="40% - 강조색6 9" xfId="222" xr:uid="{437FDFC9-C82F-4230-A465-4560C5905C74}"/>
     <cellStyle name="40% - 강조색6 9 2" xfId="548" xr:uid="{23F2E989-D1DB-40F9-8141-8F0F13CC8FC1}"/>
-    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 1" xfId="27" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 2" xfId="31" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 3" xfId="35" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 4" xfId="39" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 5" xfId="43" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 6" xfId="47" builtinId="52" customBuiltin="1"/>
     <cellStyle name="60% - 강조색1 10" xfId="228" xr:uid="{B2CB40AD-4A4F-4918-9765-E0E0363F2909}"/>
     <cellStyle name="60% - 강조색1 10 2" xfId="554" xr:uid="{716893EB-55D8-49AE-8824-F96AE98EC548}"/>
     <cellStyle name="60% - 강조색1 11" xfId="248" xr:uid="{E4397767-24DE-4A4E-8808-6EE3AC7ADD6A}"/>
@@ -8276,7 +8278,6 @@
     <cellStyle name="60% - 강조색1 8 2" xfId="514" xr:uid="{BB2511A3-C809-4350-9216-444F9C856FBF}"/>
     <cellStyle name="60% - 강조색1 9" xfId="208" xr:uid="{17F085EB-9BA6-42BC-90C0-6F0174349845}"/>
     <cellStyle name="60% - 강조색1 9 2" xfId="534" xr:uid="{8BA2814B-4D44-4E0D-BC5A-5F5D6BB08F4E}"/>
-    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36" customBuiltin="1"/>
     <cellStyle name="60% - 강조색2 10" xfId="231" xr:uid="{14C597ED-74A6-41A0-B9C3-84CD44CA0D59}"/>
     <cellStyle name="60% - 강조색2 10 2" xfId="557" xr:uid="{C2208A7B-612E-457D-AEE8-F7882A9DAAB2}"/>
     <cellStyle name="60% - 강조색2 11" xfId="251" xr:uid="{8C1F64DB-16E4-48E9-A735-71A04F737194}"/>
@@ -8308,7 +8309,6 @@
     <cellStyle name="60% - 강조색2 8 2" xfId="517" xr:uid="{62BEFE39-4CCF-4A3A-8018-6A959D2A2B4F}"/>
     <cellStyle name="60% - 강조색2 9" xfId="211" xr:uid="{A63107D2-B5A6-4F95-8B93-DE528608944A}"/>
     <cellStyle name="60% - 강조색2 9 2" xfId="537" xr:uid="{718210F5-E92E-44EF-ABF8-60C5ABA46674}"/>
-    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40" customBuiltin="1"/>
     <cellStyle name="60% - 강조색3 10" xfId="234" xr:uid="{ED75E9BB-902D-42DB-AF09-843CCDFA3E09}"/>
     <cellStyle name="60% - 강조색3 10 2" xfId="560" xr:uid="{ED026136-452A-4164-8F55-332F07E34BB5}"/>
     <cellStyle name="60% - 강조색3 11" xfId="254" xr:uid="{EA1454C4-3A62-4C0E-9767-7776B2D9DF0C}"/>
@@ -8340,7 +8340,6 @@
     <cellStyle name="60% - 강조색3 8 2" xfId="520" xr:uid="{60B19A0F-BFE3-4AE4-8768-B65FFBFE48EA}"/>
     <cellStyle name="60% - 강조색3 9" xfId="214" xr:uid="{FB8BE683-8343-4BEB-9B06-CDF01B070856}"/>
     <cellStyle name="60% - 강조색3 9 2" xfId="540" xr:uid="{20D1634B-CEAF-4453-91D3-486B1B80280E}"/>
-    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44" customBuiltin="1"/>
     <cellStyle name="60% - 강조색4 10" xfId="237" xr:uid="{70E89AC4-5EED-43E7-9ED8-EF9FC159426C}"/>
     <cellStyle name="60% - 강조색4 10 2" xfId="563" xr:uid="{CDC0EF42-7DE5-4D23-8FE6-DF68950457FF}"/>
     <cellStyle name="60% - 강조색4 11" xfId="257" xr:uid="{069866A3-60DC-46EA-9CD7-FBE3CA7D5DA3}"/>
@@ -8372,7 +8371,6 @@
     <cellStyle name="60% - 강조색4 8 2" xfId="523" xr:uid="{1DF0264B-901E-4FE6-950C-0F69F238339A}"/>
     <cellStyle name="60% - 강조색4 9" xfId="217" xr:uid="{398F5B73-4152-4111-A6C1-88930B304A8F}"/>
     <cellStyle name="60% - 강조색4 9 2" xfId="543" xr:uid="{B45702C4-B062-45FF-B097-C5EC4FC10324}"/>
-    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 강조색5 10" xfId="240" xr:uid="{A4732F92-E2E7-47F7-8962-09A53158E49E}"/>
     <cellStyle name="60% - 강조색5 10 2" xfId="566" xr:uid="{539B5567-0BBB-4CFA-ACE7-CD69405258C8}"/>
     <cellStyle name="60% - 강조색5 11" xfId="260" xr:uid="{833A5587-5E37-4DDD-A9A7-B9B835D4EEC6}"/>
@@ -8404,7 +8402,6 @@
     <cellStyle name="60% - 강조색5 8 2" xfId="526" xr:uid="{A1F6E989-7FEC-4407-BE9A-6DABCE4EA8E2}"/>
     <cellStyle name="60% - 강조색5 9" xfId="220" xr:uid="{922B3494-236E-4C09-974D-F60AAF6C7BE7}"/>
     <cellStyle name="60% - 강조색5 9 2" xfId="546" xr:uid="{E92CF570-78BA-4D31-8BF4-6427C7F120FB}"/>
-    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52" customBuiltin="1"/>
     <cellStyle name="60% - 강조색6 10" xfId="243" xr:uid="{45C2A6A0-CD21-437A-82CA-BC3AD53B6A17}"/>
     <cellStyle name="60% - 강조색6 10 2" xfId="569" xr:uid="{5FD9F675-609D-47E2-95ED-2D4BA0DC2B23}"/>
     <cellStyle name="60% - 강조색6 11" xfId="263" xr:uid="{A320767B-703A-471C-8140-F1287F2FFA6B}"/>
@@ -8454,16 +8451,24 @@
     <cellStyle name="PrePop Currency (0)" xfId="59" xr:uid="{011529D7-C760-4C88-8E9D-F1167D2FE0AB}"/>
     <cellStyle name="Text Indent A" xfId="60" xr:uid="{DBCAAEB4-FCA1-4A86-9E72-4AB119B0DF9B}"/>
     <cellStyle name="Text Indent B" xfId="61" xr:uid="{49B06124-8F30-4376-AF00-ED1364E50F8D}"/>
-    <cellStyle name="강조색1" xfId="24" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="28" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="32" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="36" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="40" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="44" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="21" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="18" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="14" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="アクセント 1" xfId="24" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="アクセント 2" xfId="28" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="アクセント 3" xfId="32" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="アクセント 4" xfId="36" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="アクセント 5" xfId="40" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="アクセント 6" xfId="44" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="タイトル" xfId="8" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="チェック セル" xfId="20" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="どちらでもない" xfId="15" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="リンク セル" xfId="19" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="見出し 1" xfId="9" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="見出し 2" xfId="10" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="見出し 3" xfId="11" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="見出し 4" xfId="12" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="警告文" xfId="21" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="計算" xfId="18" builtinId="22" customBuiltin="1"/>
     <cellStyle name="나쁨 2" xfId="365" xr:uid="{5D9ED5E1-C801-406D-93E0-2B3591175749}"/>
+    <cellStyle name="良い" xfId="13" builtinId="26" customBuiltin="1"/>
     <cellStyle name="메모 10" xfId="205" xr:uid="{F1E6B1A6-DFCC-43B5-938B-AC4EA38735C0}"/>
     <cellStyle name="메모 10 2" xfId="531" xr:uid="{94189CAC-7F9C-4DC4-AC07-5E4823A08368}"/>
     <cellStyle name="메모 11" xfId="225" xr:uid="{96156C23-3B33-4EC6-904C-30CD9C6AE460}"/>
@@ -8498,26 +8503,18 @@
     <cellStyle name="메모 9 2" xfId="511" xr:uid="{ECD9A7A6-174C-45C8-84A1-FC1D652BF901}"/>
     <cellStyle name="百分比 3" xfId="2" xr:uid="{D6C95A67-1C7B-404B-8CDF-2921498D764C}"/>
     <cellStyle name="백분율 2" xfId="49" xr:uid="{E41B836F-9572-4D1C-9D74-1056A2A9CD16}"/>
-    <cellStyle name="보통" xfId="15" builtinId="28" customBuiltin="1"/>
     <cellStyle name="보통 2" xfId="366" xr:uid="{BC2C249A-3E93-44E4-8AEE-760D3D1DF841}"/>
     <cellStyle name="常规 4" xfId="5" xr:uid="{79A5A741-AEC6-8E4D-AD07-F06A72B84B5A}"/>
     <cellStyle name="常规_8364B 2009415" xfId="48" xr:uid="{0B47AFBD-263D-4B7F-B2E7-B395D86BCEE1}"/>
-    <cellStyle name="설명 텍스트" xfId="22" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="20" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="説明文" xfId="22" builtinId="53" customBuiltin="1"/>
     <cellStyle name="쉼표 [0] 2" xfId="7" xr:uid="{404A706B-A3F0-6D4E-AC76-48F566C7C22E}"/>
     <cellStyle name="쉼표 [0] 2 2" xfId="369" xr:uid="{ADB4494C-2724-4892-8B8C-AFA06F9C5571}"/>
-    <cellStyle name="연결된 셀" xfId="19" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="悪い" xfId="14" builtinId="27" customBuiltin="1"/>
     <cellStyle name="一般 3" xfId="1" xr:uid="{CBDF56BD-CEEB-C64C-84C9-24C904CBE56D}"/>
-    <cellStyle name="입력" xfId="16" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="8" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="9" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="10" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="11" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="12" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="13" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="17" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="入力" xfId="16" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="集計" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="出力" xfId="17" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="표준 10" xfId="204" xr:uid="{97A0A5AD-B5E0-4681-B396-4D85486E02B2}"/>
     <cellStyle name="표준 10 2" xfId="530" xr:uid="{C702AF46-07B9-49A9-BBB8-0A57A31041F3}"/>
     <cellStyle name="표준 11" xfId="224" xr:uid="{DCBD210C-C26C-487C-AAFF-E96EFCCBF417}"/>
@@ -8603,26 +8600,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="1213 Y"/>
-    </sheetNames>
-    <definedNames>
-      <definedName name="ㅂㅂㅂ"/>
-    </definedNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8660,7 +8641,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -8766,7 +8747,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8908,7 +8889,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -8918,33 +8899,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A681568-1FAC-2B47-9C47-A4A560421BB4}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:J53"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="15"/>
-    <col min="2" max="2" width="13.81640625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="30.81640625" style="15" customWidth="1"/>
-    <col min="4" max="5" width="25.81640625" style="15" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" style="15"/>
-    <col min="8" max="9" width="10.81640625" style="15" customWidth="1"/>
-    <col min="10" max="16384" width="10.81640625" style="15"/>
+    <col min="1" max="1" width="10.77734375" style="15"/>
+    <col min="2" max="2" width="13.77734375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" style="15" customWidth="1"/>
+    <col min="4" max="5" width="25.77734375" style="15" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" style="15"/>
+    <col min="8" max="9" width="10.77734375" style="15" customWidth="1"/>
+    <col min="10" max="16384" width="10.77734375" style="15"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="40.200000000000003" customHeight="1">
+    <row r="2" spans="1:10" ht="40.15" customHeight="1">
       <c r="A2" s="8"/>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
     </row>
-    <row r="3" spans="1:10" ht="16.2" customHeight="1">
+    <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -8956,7 +8937,7 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" ht="16.2" customHeight="1">
+    <row r="4" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="11" t="s">
@@ -8972,7 +8953,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" spans="1:10" ht="16.2" customHeight="1">
+    <row r="5" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -8990,7 +8971,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" ht="16.2" customHeight="1">
+    <row r="6" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>0</v>
@@ -9059,7 +9040,7 @@
       <c r="E9" s="112">
         <v>0</v>
       </c>
-      <c r="F9" s="117" t="s">
+      <c r="F9" s="121" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="4"/>
@@ -9081,7 +9062,7 @@
         <f>E8</f>
         <v>480</v>
       </c>
-      <c r="F10" s="117"/>
+      <c r="F10" s="121"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -9096,13 +9077,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4"/>
-      <c r="B12" s="118" t="s">
+      <c r="B12" s="122" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="118"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -9132,7 +9113,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="10"/>
-      <c r="B14" s="115" t="s">
+      <c r="B14" s="119" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6"/>
@@ -9142,7 +9123,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="10"/>
-      <c r="B15" s="115"/>
+      <c r="B15" s="119"/>
       <c r="C15" s="6"/>
       <c r="D15" s="7"/>
       <c r="E15" s="9"/>
@@ -9150,7 +9131,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="10"/>
-      <c r="B16" s="115"/>
+      <c r="B16" s="119"/>
       <c r="C16" s="6"/>
       <c r="D16" s="7"/>
       <c r="E16" s="9"/>
@@ -9158,7 +9139,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="10"/>
-      <c r="B17" s="115"/>
+      <c r="B17" s="119"/>
       <c r="C17" s="6"/>
       <c r="D17" s="7"/>
       <c r="E17" s="9"/>
@@ -9166,7 +9147,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="10"/>
-      <c r="B18" s="115"/>
+      <c r="B18" s="119"/>
       <c r="C18" s="6"/>
       <c r="D18" s="7"/>
       <c r="E18" s="9"/>
@@ -9174,7 +9155,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="10"/>
-      <c r="B19" s="115"/>
+      <c r="B19" s="119"/>
       <c r="C19" s="6"/>
       <c r="D19" s="7"/>
       <c r="E19" s="9"/>
@@ -9182,7 +9163,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="10"/>
-      <c r="B20" s="115"/>
+      <c r="B20" s="119"/>
       <c r="C20" s="6"/>
       <c r="D20" s="7"/>
       <c r="E20" s="9"/>
@@ -9190,7 +9171,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="10"/>
-      <c r="B21" s="115"/>
+      <c r="B21" s="119"/>
       <c r="C21" s="6"/>
       <c r="D21" s="7"/>
       <c r="E21" s="9"/>
@@ -9198,7 +9179,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="10"/>
-      <c r="B22" s="115"/>
+      <c r="B22" s="119"/>
       <c r="C22" s="6"/>
       <c r="D22" s="7"/>
       <c r="E22" s="9"/>
@@ -9206,7 +9187,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="10"/>
-      <c r="B23" s="115"/>
+      <c r="B23" s="119"/>
       <c r="C23" s="6"/>
       <c r="D23" s="7"/>
       <c r="E23" s="9"/>
@@ -9214,7 +9195,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="10"/>
-      <c r="B24" s="115" t="s">
+      <c r="B24" s="119" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="6"/>
@@ -9224,7 +9205,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="10"/>
-      <c r="B25" s="115"/>
+      <c r="B25" s="119"/>
       <c r="C25" s="6"/>
       <c r="D25" s="13"/>
       <c r="E25" s="18"/>
@@ -9232,7 +9213,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="10"/>
-      <c r="B26" s="115"/>
+      <c r="B26" s="119"/>
       <c r="C26" s="6"/>
       <c r="D26" s="13"/>
       <c r="E26" s="18"/>
@@ -9240,7 +9221,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="16"/>
-      <c r="B27" s="115"/>
+      <c r="B27" s="119"/>
       <c r="C27" s="6"/>
       <c r="D27" s="13"/>
       <c r="E27" s="18"/>
@@ -9248,7 +9229,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="16"/>
-      <c r="B28" s="115"/>
+      <c r="B28" s="119"/>
       <c r="C28" s="6"/>
       <c r="D28" s="13"/>
       <c r="E28" s="18"/>
@@ -9256,7 +9237,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="16"/>
-      <c r="B29" s="115"/>
+      <c r="B29" s="119"/>
       <c r="C29" s="6"/>
       <c r="D29" s="13"/>
       <c r="E29" s="18"/>
@@ -9264,7 +9245,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="16"/>
-      <c r="B30" s="115"/>
+      <c r="B30" s="119"/>
       <c r="C30" s="6"/>
       <c r="D30" s="13"/>
       <c r="E30" s="18"/>
@@ -9272,7 +9253,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="16"/>
-      <c r="B31" s="115"/>
+      <c r="B31" s="119"/>
       <c r="C31" s="6"/>
       <c r="D31" s="13"/>
       <c r="E31" s="18"/>
@@ -9280,7 +9261,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="16"/>
-      <c r="B32" s="115"/>
+      <c r="B32" s="119"/>
       <c r="C32" s="6"/>
       <c r="D32" s="13"/>
       <c r="E32" s="18"/>
@@ -9288,7 +9269,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="16"/>
-      <c r="B33" s="115"/>
+      <c r="B33" s="119"/>
       <c r="C33" s="6"/>
       <c r="D33" s="13"/>
       <c r="E33" s="18"/>
@@ -9296,7 +9277,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="16"/>
-      <c r="B34" s="115" t="s">
+      <c r="B34" s="119" t="s">
         <v>13</v>
       </c>
       <c r="C34" s="6"/>
@@ -9306,7 +9287,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="16"/>
-      <c r="B35" s="115"/>
+      <c r="B35" s="119"/>
       <c r="C35" s="6"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -9314,7 +9295,7 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="16"/>
-      <c r="B36" s="115"/>
+      <c r="B36" s="119"/>
       <c r="C36" s="6"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -9322,7 +9303,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="16"/>
-      <c r="B37" s="115"/>
+      <c r="B37" s="119"/>
       <c r="C37" s="6"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -9330,7 +9311,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="16"/>
-      <c r="B38" s="115"/>
+      <c r="B38" s="119"/>
       <c r="C38" s="6"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -9338,7 +9319,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="16"/>
-      <c r="B39" s="115"/>
+      <c r="B39" s="119"/>
       <c r="C39" s="6"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -9346,7 +9327,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="16"/>
-      <c r="B40" s="115"/>
+      <c r="B40" s="119"/>
       <c r="C40" s="6"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -9354,7 +9335,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="16"/>
-      <c r="B41" s="115"/>
+      <c r="B41" s="119"/>
       <c r="C41" s="6"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -9362,7 +9343,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="16"/>
-      <c r="B42" s="115"/>
+      <c r="B42" s="119"/>
       <c r="C42" s="6"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -9370,14 +9351,14 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="16"/>
-      <c r="B43" s="115"/>
+      <c r="B43" s="119"/>
       <c r="C43" s="6"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="13"/>
     </row>
     <row r="44" spans="1:6">
-      <c r="B44" s="114" t="s">
+      <c r="B44" s="118" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="6"/>
@@ -9386,63 +9367,63 @@
       <c r="F44" s="13"/>
     </row>
     <row r="45" spans="1:6">
-      <c r="B45" s="114"/>
+      <c r="B45" s="118"/>
       <c r="C45" s="6"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="13"/>
     </row>
     <row r="46" spans="1:6">
-      <c r="B46" s="114"/>
+      <c r="B46" s="118"/>
       <c r="C46" s="6"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="13"/>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="114"/>
+      <c r="B47" s="118"/>
       <c r="C47" s="6"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="13"/>
     </row>
     <row r="48" spans="1:6">
-      <c r="B48" s="114"/>
+      <c r="B48" s="118"/>
       <c r="C48" s="6"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="13"/>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="114"/>
+      <c r="B49" s="118"/>
       <c r="C49" s="6"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="13"/>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="114"/>
+      <c r="B50" s="118"/>
       <c r="C50" s="6"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="13"/>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="114"/>
+      <c r="B51" s="118"/>
       <c r="C51" s="6"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
       <c r="F51" s="13"/>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="114"/>
+      <c r="B52" s="118"/>
       <c r="C52" s="6"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="F52" s="13"/>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="114"/>
+      <c r="B53" s="118"/>
       <c r="C53" s="6"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
@@ -9467,18 +9448,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E0A30F-D12B-F646-9C85-8B37D7BCD295}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="2" width="17.6328125" style="92" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" style="92" customWidth="1"/>
-    <col min="4" max="4" width="17.6328125" style="92" customWidth="1"/>
-    <col min="5" max="5" width="40.6328125" style="92" customWidth="1"/>
-    <col min="6" max="6" width="17.6328125" style="92" customWidth="1"/>
-    <col min="7" max="7" width="12.6328125" style="92" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" style="93" customWidth="1"/>
-    <col min="9" max="10" width="12.6328125" style="92" customWidth="1"/>
-    <col min="11" max="11" width="10.90625" style="92"/>
-    <col min="13" max="16384" width="10.90625" style="92"/>
+    <col min="1" max="2" width="17.6640625" style="92" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="92" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="92" customWidth="1"/>
+    <col min="5" max="5" width="40.6640625" style="92" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" style="92" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="92" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="93" customWidth="1"/>
+    <col min="9" max="10" width="12.6640625" style="92" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" style="92"/>
+    <col min="13" max="16384" width="10.88671875" style="92"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -9513,7 +9494,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="19.2" customHeight="1">
+    <row r="2" spans="1:10" ht="19.149999999999999" customHeight="1">
       <c r="A2" s="98" t="s">
         <v>257</v>
       </c>
@@ -9591,40 +9572,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0923581-E588-B346-A92D-CE7EA704E921}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:T153"/>
-  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="12.44140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="0.81640625" style="21" customWidth="1"/>
+    <col min="1" max="1" width="0.77734375" style="21" customWidth="1"/>
     <col min="2" max="2" width="9" style="21" customWidth="1"/>
     <col min="3" max="3" width="13" style="21" customWidth="1"/>
     <col min="4" max="18" width="9" style="21" customWidth="1"/>
-    <col min="19" max="19" width="13.1796875" style="21" customWidth="1"/>
-    <col min="20" max="16384" width="12.453125" style="21"/>
+    <col min="19" max="19" width="13.21875" style="21" customWidth="1"/>
+    <col min="20" max="16384" width="12.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21">
-      <c r="A1" s="119" t="s">
+    <row r="1" spans="1:20" ht="20.25">
+      <c r="A1" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="123"/>
     </row>
-    <row r="2" spans="1:20" ht="10.199999999999999" customHeight="1">
+    <row r="2" spans="1:20" ht="10.15" customHeight="1">
       <c r="A2" s="20"/>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -9647,64 +9628,64 @@
     </row>
     <row r="3" spans="1:20" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="22"/>
-      <c r="B3" s="120" t="s">
+      <c r="B3" s="124" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="121" t="s">
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="122" t="s">
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="121"/>
-      <c r="P3" s="121"/>
-      <c r="Q3" s="121"/>
-      <c r="R3" s="123"/>
-      <c r="S3" s="124" t="s">
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="128" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1">
       <c r="A4" s="24"/>
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="124" t="s">
+      <c r="C4" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="125" t="s">
+      <c r="D4" s="129" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="126" t="s">
+      <c r="E4" s="130" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="126" t="s">
+      <c r="F4" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="129" t="s">
+      <c r="G4" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="130" t="s">
+      <c r="H4" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="131" t="s">
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="127" t="s">
+      <c r="L4" s="134"/>
+      <c r="M4" s="134"/>
+      <c r="N4" s="131" t="s">
         <v>38</v>
       </c>
       <c r="O4" s="25" t="s">
@@ -9715,16 +9696,16 @@
         <v>40</v>
       </c>
       <c r="R4" s="26"/>
-      <c r="S4" s="124"/>
+      <c r="S4" s="128"/>
     </row>
     <row r="5" spans="1:20" ht="18" customHeight="1">
       <c r="A5" s="28"/>
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="129"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="133"/>
       <c r="H5" s="43"/>
       <c r="I5" s="43"/>
       <c r="J5" s="43"/>
@@ -9737,7 +9718,7 @@
       <c r="M5" s="43">
         <v>3</v>
       </c>
-      <c r="N5" s="128"/>
+      <c r="N5" s="132"/>
       <c r="O5" s="36" t="s">
         <v>41</v>
       </c>
@@ -9750,7 +9731,7 @@
       <c r="R5" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="S5" s="124"/>
+      <c r="S5" s="128"/>
     </row>
     <row r="6" spans="1:20" ht="18" customHeight="1">
       <c r="A6" s="29"/>
@@ -9760,13 +9741,13 @@
       <c r="C6" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="141">
+      <c r="D6" s="114">
         <v>0.5</v>
       </c>
-      <c r="E6" s="141">
+      <c r="E6" s="114">
         <v>0.01</v>
       </c>
-      <c r="F6" s="141">
+      <c r="F6" s="114">
         <v>-0.01</v>
       </c>
       <c r="G6" s="38" t="s">
@@ -9818,13 +9799,13 @@
       <c r="C7" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="141">
+      <c r="D7" s="114">
         <v>0.5</v>
       </c>
-      <c r="E7" s="141">
+      <c r="E7" s="114">
         <v>0.01</v>
       </c>
-      <c r="F7" s="141">
+      <c r="F7" s="114">
         <v>-0.01</v>
       </c>
       <c r="G7" s="38" t="s">
@@ -9876,13 +9857,13 @@
       <c r="C8" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="141">
+      <c r="D8" s="114">
         <v>0.5</v>
       </c>
-      <c r="E8" s="141">
+      <c r="E8" s="114">
         <v>0.01</v>
       </c>
-      <c r="F8" s="141">
+      <c r="F8" s="114">
         <v>-0.01</v>
       </c>
       <c r="G8" s="38" t="s">
@@ -9934,13 +9915,13 @@
       <c r="C9" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="141">
-        <v>0</v>
-      </c>
-      <c r="E9" s="141">
+      <c r="D9" s="114">
+        <v>0</v>
+      </c>
+      <c r="E9" s="114">
         <v>0.02</v>
       </c>
-      <c r="F9" s="141">
+      <c r="F9" s="114">
         <v>0</v>
       </c>
       <c r="G9" s="38" t="s">
@@ -9992,13 +9973,13 @@
       <c r="C10" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="141">
-        <v>0</v>
-      </c>
-      <c r="E10" s="141">
+      <c r="D10" s="114">
+        <v>0</v>
+      </c>
+      <c r="E10" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F10" s="141">
+      <c r="F10" s="114">
         <v>0</v>
       </c>
       <c r="G10" s="38" t="s">
@@ -10050,13 +10031,13 @@
       <c r="C11" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="141">
-        <v>0</v>
-      </c>
-      <c r="E11" s="141">
+      <c r="D11" s="114">
+        <v>0</v>
+      </c>
+      <c r="E11" s="114">
         <v>0.02</v>
       </c>
-      <c r="F11" s="141">
+      <c r="F11" s="114">
         <v>0</v>
       </c>
       <c r="G11" s="38" t="s">
@@ -10108,13 +10089,13 @@
       <c r="C12" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="141">
+      <c r="D12" s="114">
         <v>12.612</v>
       </c>
-      <c r="E12" s="141">
+      <c r="E12" s="114">
         <v>0.02</v>
       </c>
-      <c r="F12" s="141">
+      <c r="F12" s="114">
         <v>-0.02</v>
       </c>
       <c r="G12" s="38" t="s">
@@ -10166,13 +10147,13 @@
       <c r="C13" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="141">
+      <c r="D13" s="114">
         <v>0.04</v>
       </c>
-      <c r="E13" s="141">
+      <c r="E13" s="114">
         <v>0.02</v>
       </c>
-      <c r="F13" s="141">
+      <c r="F13" s="114">
         <v>-0.02</v>
       </c>
       <c r="G13" s="38" t="s">
@@ -10224,13 +10205,13 @@
       <c r="C14" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="141">
+      <c r="D14" s="114">
         <v>0.04</v>
       </c>
-      <c r="E14" s="141">
+      <c r="E14" s="114">
         <v>0.02</v>
       </c>
-      <c r="F14" s="141">
+      <c r="F14" s="114">
         <v>-0.02</v>
       </c>
       <c r="G14" s="38" t="s">
@@ -10282,13 +10263,13 @@
       <c r="C15" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="141">
+      <c r="D15" s="114">
         <v>12.382</v>
       </c>
-      <c r="E15" s="141">
+      <c r="E15" s="114">
         <v>0.02</v>
       </c>
-      <c r="F15" s="141">
+      <c r="F15" s="114">
         <v>-0.02</v>
       </c>
       <c r="G15" s="38" t="s">
@@ -10340,13 +10321,13 @@
       <c r="C16" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="141">
+      <c r="D16" s="114">
         <v>14.726000000000001</v>
       </c>
-      <c r="E16" s="141">
+      <c r="E16" s="114">
         <v>0.02</v>
       </c>
-      <c r="F16" s="141">
+      <c r="F16" s="114">
         <v>-0.02</v>
       </c>
       <c r="G16" s="38" t="s">
@@ -10398,13 +10379,13 @@
       <c r="C17" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="141">
+      <c r="D17" s="114">
         <v>14.506</v>
       </c>
-      <c r="E17" s="141">
+      <c r="E17" s="114">
         <v>0.02</v>
       </c>
-      <c r="F17" s="141">
+      <c r="F17" s="114">
         <v>-0.02</v>
       </c>
       <c r="G17" s="38" t="s">
@@ -10456,13 +10437,13 @@
       <c r="C18" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="141">
+      <c r="D18" s="114">
         <v>0.05</v>
       </c>
-      <c r="E18" s="141">
+      <c r="E18" s="114">
         <v>0.02</v>
       </c>
-      <c r="F18" s="141">
+      <c r="F18" s="114">
         <v>-0.02</v>
       </c>
       <c r="G18" s="38" t="s">
@@ -10514,13 +10495,13 @@
       <c r="C19" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="141">
+      <c r="D19" s="114">
         <v>0.05</v>
       </c>
-      <c r="E19" s="141">
+      <c r="E19" s="114">
         <v>0.02</v>
       </c>
-      <c r="F19" s="141">
+      <c r="F19" s="114">
         <v>-0.02</v>
       </c>
       <c r="G19" s="38" t="s">
@@ -10572,13 +10553,13 @@
       <c r="C20" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="141">
+      <c r="D20" s="114">
         <v>9.9190000000000005</v>
       </c>
-      <c r="E20" s="141">
+      <c r="E20" s="114">
         <v>0.02</v>
       </c>
-      <c r="F20" s="141">
+      <c r="F20" s="114">
         <v>-0.02</v>
       </c>
       <c r="G20" s="38" t="s">
@@ -10630,13 +10611,13 @@
       <c r="C21" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="141">
+      <c r="D21" s="114">
         <v>9.9190000000000005</v>
       </c>
-      <c r="E21" s="141">
+      <c r="E21" s="114">
         <v>0.02</v>
       </c>
-      <c r="F21" s="141">
+      <c r="F21" s="114">
         <v>-0.02</v>
       </c>
       <c r="G21" s="38" t="s">
@@ -10688,13 +10669,13 @@
       <c r="C22" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="141">
+      <c r="D22" s="114">
         <v>9.9190000000000005</v>
       </c>
-      <c r="E22" s="141">
+      <c r="E22" s="114">
         <v>0.02</v>
       </c>
-      <c r="F22" s="141">
+      <c r="F22" s="114">
         <v>-0.02</v>
       </c>
       <c r="G22" s="38" t="s">
@@ -10746,13 +10727,13 @@
       <c r="C23" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="141">
+      <c r="D23" s="114">
         <v>12.795</v>
       </c>
-      <c r="E23" s="141">
+      <c r="E23" s="114">
         <v>0.02</v>
       </c>
-      <c r="F23" s="141">
+      <c r="F23" s="114">
         <v>-0.02</v>
       </c>
       <c r="G23" s="38" t="s">
@@ -10804,13 +10785,13 @@
       <c r="C24" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="141">
+      <c r="D24" s="114">
         <v>12.795</v>
       </c>
-      <c r="E24" s="141">
+      <c r="E24" s="114">
         <v>0.02</v>
       </c>
-      <c r="F24" s="141">
+      <c r="F24" s="114">
         <v>-0.02</v>
       </c>
       <c r="G24" s="38" t="s">
@@ -10862,13 +10843,13 @@
       <c r="C25" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="141">
+      <c r="D25" s="114">
         <v>12.795</v>
       </c>
-      <c r="E25" s="141">
+      <c r="E25" s="114">
         <v>0.02</v>
       </c>
-      <c r="F25" s="141">
+      <c r="F25" s="114">
         <v>-0.02</v>
       </c>
       <c r="G25" s="38" t="s">
@@ -10920,13 +10901,13 @@
       <c r="C26" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="141">
+      <c r="D26" s="114">
         <v>0.105</v>
       </c>
-      <c r="E26" s="141">
+      <c r="E26" s="114">
         <v>0.02</v>
       </c>
-      <c r="F26" s="141">
+      <c r="F26" s="114">
         <v>-0.02</v>
       </c>
       <c r="G26" s="38" t="s">
@@ -10978,13 +10959,13 @@
       <c r="C27" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="141">
+      <c r="D27" s="114">
         <v>0.105</v>
       </c>
-      <c r="E27" s="141">
+      <c r="E27" s="114">
         <v>0.02</v>
       </c>
-      <c r="F27" s="141">
+      <c r="F27" s="114">
         <v>-0.02</v>
       </c>
       <c r="G27" s="38" t="s">
@@ -11036,13 +11017,13 @@
       <c r="C28" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="141">
+      <c r="D28" s="114">
         <v>0.91</v>
       </c>
-      <c r="E28" s="141">
+      <c r="E28" s="114">
         <v>0.02</v>
       </c>
-      <c r="F28" s="141">
+      <c r="F28" s="114">
         <v>-0.02</v>
       </c>
       <c r="G28" s="38" t="s">
@@ -11094,13 +11075,13 @@
       <c r="C29" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="141">
+      <c r="D29" s="114">
         <v>0.91</v>
       </c>
-      <c r="E29" s="141">
+      <c r="E29" s="114">
         <v>0.02</v>
       </c>
-      <c r="F29" s="141">
+      <c r="F29" s="114">
         <v>-0.02</v>
       </c>
       <c r="G29" s="38" t="s">
@@ -11152,13 +11133,13 @@
       <c r="C30" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="141">
+      <c r="D30" s="114">
         <v>0.91</v>
       </c>
-      <c r="E30" s="141">
+      <c r="E30" s="114">
         <v>0.02</v>
       </c>
-      <c r="F30" s="141">
+      <c r="F30" s="114">
         <v>-0.02</v>
       </c>
       <c r="G30" s="38" t="s">
@@ -11210,13 +11191,13 @@
       <c r="C31" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="141">
+      <c r="D31" s="114">
         <v>0.86</v>
       </c>
-      <c r="E31" s="141">
+      <c r="E31" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F31" s="141">
+      <c r="F31" s="114">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G31" s="38" t="s">
@@ -11268,13 +11249,13 @@
       <c r="C32" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="141">
+      <c r="D32" s="114">
         <v>0.86</v>
       </c>
-      <c r="E32" s="141">
+      <c r="E32" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F32" s="141">
+      <c r="F32" s="114">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G32" s="38" t="s">
@@ -11326,13 +11307,13 @@
       <c r="C33" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="141">
+      <c r="D33" s="114">
         <v>0.86</v>
       </c>
-      <c r="E33" s="141">
+      <c r="E33" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F33" s="141">
+      <c r="F33" s="114">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G33" s="38" t="s">
@@ -11384,13 +11365,13 @@
       <c r="C34" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="141">
+      <c r="D34" s="114">
         <v>0.87</v>
       </c>
-      <c r="E34" s="141">
+      <c r="E34" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F34" s="141">
+      <c r="F34" s="114">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G34" s="38" t="s">
@@ -11436,13 +11417,13 @@
       <c r="C35" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D35" s="141">
+      <c r="D35" s="114">
         <v>0.87</v>
       </c>
-      <c r="E35" s="141">
+      <c r="E35" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F35" s="141">
+      <c r="F35" s="114">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G35" s="38" t="s">
@@ -11494,13 +11475,13 @@
       <c r="C36" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D36" s="141">
+      <c r="D36" s="114">
         <v>12.561999999999999</v>
       </c>
-      <c r="E36" s="141">
+      <c r="E36" s="114">
         <v>0.02</v>
       </c>
-      <c r="F36" s="141">
+      <c r="F36" s="114">
         <v>-0.02</v>
       </c>
       <c r="G36" s="38" t="s">
@@ -11552,13 +11533,13 @@
       <c r="C37" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="141">
+      <c r="D37" s="114">
         <v>12.332000000000001</v>
       </c>
-      <c r="E37" s="141">
+      <c r="E37" s="114">
         <v>0.02</v>
       </c>
-      <c r="F37" s="141">
+      <c r="F37" s="114">
         <v>-0.02</v>
       </c>
       <c r="G37" s="38" t="s">
@@ -11610,13 +11591,13 @@
       <c r="C38" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D38" s="141">
+      <c r="D38" s="114">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E38" s="141">
+      <c r="E38" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F38" s="141">
+      <c r="F38" s="114">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G38" s="38" t="s">
@@ -11668,13 +11649,13 @@
       <c r="C39" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D39" s="141">
+      <c r="D39" s="114">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E39" s="141">
+      <c r="E39" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F39" s="141">
+      <c r="F39" s="114">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G39" s="38" t="s">
@@ -11726,13 +11707,13 @@
       <c r="C40" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="141">
+      <c r="D40" s="114">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E40" s="141">
+      <c r="E40" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F40" s="141">
+      <c r="F40" s="114">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G40" s="38" t="s">
@@ -11784,13 +11765,13 @@
       <c r="C41" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D41" s="141">
+      <c r="D41" s="114">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E41" s="141">
+      <c r="E41" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F41" s="141">
+      <c r="F41" s="114">
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G41" s="38" t="s">
@@ -11842,13 +11823,13 @@
       <c r="C42" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D42" s="141">
+      <c r="D42" s="114">
         <v>0.96299999999999997</v>
       </c>
-      <c r="E42" s="141">
+      <c r="E42" s="114">
         <v>0.02</v>
       </c>
-      <c r="F42" s="141">
+      <c r="F42" s="114">
         <v>-0.02</v>
       </c>
       <c r="G42" s="38" t="s">
@@ -11900,13 +11881,13 @@
       <c r="C43" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="141">
+      <c r="D43" s="114">
         <v>1.58</v>
       </c>
-      <c r="E43" s="141">
+      <c r="E43" s="114">
         <v>0.02</v>
       </c>
-      <c r="F43" s="141">
+      <c r="F43" s="114">
         <v>-0.02</v>
       </c>
       <c r="G43" s="38" t="s">
@@ -11958,13 +11939,13 @@
       <c r="C44" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D44" s="141">
+      <c r="D44" s="114">
         <v>1.85</v>
       </c>
-      <c r="E44" s="141">
+      <c r="E44" s="114">
         <v>0.02</v>
       </c>
-      <c r="F44" s="141">
+      <c r="F44" s="114">
         <v>-0.02</v>
       </c>
       <c r="G44" s="38" t="s">
@@ -12016,13 +11997,13 @@
       <c r="C45" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D45" s="141">
+      <c r="D45" s="114">
         <v>1.85</v>
       </c>
-      <c r="E45" s="141">
+      <c r="E45" s="114">
         <v>0.02</v>
       </c>
-      <c r="F45" s="141">
+      <c r="F45" s="114">
         <v>-0.02</v>
       </c>
       <c r="G45" s="38" t="s">
@@ -12074,13 +12055,13 @@
       <c r="C46" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="141">
+      <c r="D46" s="114">
         <v>6.9009999999999998</v>
       </c>
-      <c r="E46" s="141">
+      <c r="E46" s="114">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F46" s="141">
+      <c r="F46" s="114">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="G46" s="38" t="s">
@@ -12132,13 +12113,13 @@
       <c r="C47" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D47" s="141">
+      <c r="D47" s="114">
         <v>6.9009999999999998</v>
       </c>
-      <c r="E47" s="141">
+      <c r="E47" s="114">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F47" s="141">
+      <c r="F47" s="114">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="G47" s="38" t="s">
@@ -12190,13 +12171,13 @@
       <c r="C48" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D48" s="141">
+      <c r="D48" s="114">
         <v>6.9009999999999998</v>
       </c>
-      <c r="E48" s="141">
+      <c r="E48" s="114">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F48" s="141">
+      <c r="F48" s="114">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="G48" s="38" t="s">
@@ -12248,13 +12229,13 @@
       <c r="C49" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D49" s="141">
+      <c r="D49" s="114">
         <v>2.9729999999999999</v>
       </c>
-      <c r="E49" s="141">
+      <c r="E49" s="114">
         <v>0.02</v>
       </c>
-      <c r="F49" s="141">
+      <c r="F49" s="114">
         <v>-0.02</v>
       </c>
       <c r="G49" s="38" t="s">
@@ -12306,13 +12287,13 @@
       <c r="C50" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D50" s="141">
+      <c r="D50" s="114">
         <v>2.9729999999999999</v>
       </c>
-      <c r="E50" s="141">
+      <c r="E50" s="114">
         <v>0.02</v>
       </c>
-      <c r="F50" s="141">
+      <c r="F50" s="114">
         <v>-0.02</v>
       </c>
       <c r="G50" s="38" t="s">
@@ -12364,13 +12345,13 @@
       <c r="C51" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D51" s="141">
+      <c r="D51" s="114">
         <v>2.9729999999999999</v>
       </c>
-      <c r="E51" s="141">
+      <c r="E51" s="114">
         <v>0.02</v>
       </c>
-      <c r="F51" s="141">
+      <c r="F51" s="114">
         <v>-0.02</v>
       </c>
       <c r="G51" s="38" t="s">
@@ -12422,13 +12403,13 @@
       <c r="C52" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="141">
+      <c r="D52" s="114">
         <v>4.532</v>
       </c>
-      <c r="E52" s="141">
+      <c r="E52" s="114">
         <v>0.03</v>
       </c>
-      <c r="F52" s="141">
+      <c r="F52" s="114">
         <v>-0.03</v>
       </c>
       <c r="G52" s="38" t="s">
@@ -12480,13 +12461,13 @@
       <c r="C53" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D53" s="141">
+      <c r="D53" s="114">
         <v>7.8010000000000002</v>
       </c>
-      <c r="E53" s="141">
+      <c r="E53" s="114">
         <v>0.03</v>
       </c>
-      <c r="F53" s="141">
+      <c r="F53" s="114">
         <v>-0.03</v>
       </c>
       <c r="G53" s="38" t="s">
@@ -12538,13 +12519,13 @@
       <c r="C54" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D54" s="141">
+      <c r="D54" s="114">
         <v>7.8010000000000002</v>
       </c>
-      <c r="E54" s="141">
+      <c r="E54" s="114">
         <v>0.03</v>
       </c>
-      <c r="F54" s="141">
+      <c r="F54" s="114">
         <v>-0.03</v>
       </c>
       <c r="G54" s="38" t="s">
@@ -12596,13 +12577,13 @@
       <c r="C55" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D55" s="141">
+      <c r="D55" s="114">
         <v>7.8010000000000002</v>
       </c>
-      <c r="E55" s="141">
+      <c r="E55" s="114">
         <v>0.03</v>
       </c>
-      <c r="F55" s="141">
+      <c r="F55" s="114">
         <v>-0.03</v>
       </c>
       <c r="G55" s="38" t="s">
@@ -12654,13 +12635,13 @@
       <c r="C56" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D56" s="141">
+      <c r="D56" s="114">
         <v>10.154999999999999</v>
       </c>
-      <c r="E56" s="141">
+      <c r="E56" s="114">
         <v>0.03</v>
       </c>
-      <c r="F56" s="141">
+      <c r="F56" s="114">
         <v>-0.03</v>
       </c>
       <c r="G56" s="38" t="s">
@@ -12712,13 +12693,13 @@
       <c r="C57" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D57" s="141">
+      <c r="D57" s="114">
         <v>10.154999999999999</v>
       </c>
-      <c r="E57" s="141">
+      <c r="E57" s="114">
         <v>0.03</v>
       </c>
-      <c r="F57" s="141">
+      <c r="F57" s="114">
         <v>-0.03</v>
       </c>
       <c r="G57" s="38" t="s">
@@ -12770,13 +12751,13 @@
       <c r="C58" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D58" s="141">
+      <c r="D58" s="114">
         <v>8.1950000000000003</v>
       </c>
-      <c r="E58" s="141">
+      <c r="E58" s="114">
         <v>0.03</v>
       </c>
-      <c r="F58" s="141">
+      <c r="F58" s="114">
         <v>-0.03</v>
       </c>
       <c r="G58" s="38" t="s">
@@ -12828,13 +12809,13 @@
       <c r="C59" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D59" s="141">
+      <c r="D59" s="114">
         <v>0.626</v>
       </c>
-      <c r="E59" s="141">
+      <c r="E59" s="114">
         <v>0.02</v>
       </c>
-      <c r="F59" s="141">
+      <c r="F59" s="114">
         <v>-0.02</v>
       </c>
       <c r="G59" s="38" t="s">
@@ -12886,13 +12867,13 @@
       <c r="C60" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D60" s="141">
+      <c r="D60" s="114">
         <v>0.626</v>
       </c>
-      <c r="E60" s="141">
+      <c r="E60" s="114">
         <v>0.02</v>
       </c>
-      <c r="F60" s="141">
+      <c r="F60" s="114">
         <v>-0.02</v>
       </c>
       <c r="G60" s="38" t="s">
@@ -12944,13 +12925,13 @@
       <c r="C61" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D61" s="141">
+      <c r="D61" s="114">
         <v>1.9530000000000001</v>
       </c>
-      <c r="E61" s="141">
+      <c r="E61" s="114">
         <v>0.03</v>
       </c>
-      <c r="F61" s="141">
+      <c r="F61" s="114">
         <v>-0.03</v>
       </c>
       <c r="G61" s="38" t="s">
@@ -13002,13 +12983,13 @@
       <c r="C62" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D62" s="141">
+      <c r="D62" s="114">
         <v>1.9530000000000001</v>
       </c>
-      <c r="E62" s="141">
+      <c r="E62" s="114">
         <v>0.03</v>
       </c>
-      <c r="F62" s="141">
+      <c r="F62" s="114">
         <v>-0.03</v>
       </c>
       <c r="G62" s="38" t="s">
@@ -13060,13 +13041,13 @@
       <c r="C63" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D63" s="141">
+      <c r="D63" s="114">
         <v>2.9260000000000002</v>
       </c>
-      <c r="E63" s="141">
+      <c r="E63" s="114">
         <v>0.03</v>
       </c>
-      <c r="F63" s="141">
+      <c r="F63" s="114">
         <v>-0.03</v>
       </c>
       <c r="G63" s="38" t="s">
@@ -13118,13 +13099,13 @@
       <c r="C64" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D64" s="141">
+      <c r="D64" s="114">
         <v>2.8730000000000002</v>
       </c>
-      <c r="E64" s="141">
+      <c r="E64" s="114">
         <v>0.03</v>
       </c>
-      <c r="F64" s="141">
+      <c r="F64" s="114">
         <v>-0.03</v>
       </c>
       <c r="G64" s="38" t="s">
@@ -13176,13 +13157,13 @@
       <c r="C65" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D65" s="141">
+      <c r="D65" s="114">
         <v>0.97799999999999998</v>
       </c>
-      <c r="E65" s="141">
+      <c r="E65" s="114">
         <v>0.03</v>
       </c>
-      <c r="F65" s="141">
+      <c r="F65" s="114">
         <v>-0.03</v>
       </c>
       <c r="G65" s="38" t="s">
@@ -13234,13 +13215,13 @@
       <c r="C66" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D66" s="141">
+      <c r="D66" s="114">
         <v>0.98499999999999999</v>
       </c>
-      <c r="E66" s="141">
+      <c r="E66" s="114">
         <v>0.03</v>
       </c>
-      <c r="F66" s="141">
+      <c r="F66" s="114">
         <v>-0.03</v>
       </c>
       <c r="G66" s="38" t="s">
@@ -13292,13 +13273,13 @@
       <c r="C67" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D67" s="141">
+      <c r="D67" s="114">
         <v>4.5339999999999998</v>
       </c>
-      <c r="E67" s="141">
+      <c r="E67" s="114">
         <v>0.03</v>
       </c>
-      <c r="F67" s="141">
+      <c r="F67" s="114">
         <v>-0.03</v>
       </c>
       <c r="G67" s="38" t="s">
@@ -13350,13 +13331,13 @@
       <c r="C68" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D68" s="141">
+      <c r="D68" s="114">
         <v>6.9379999999999997</v>
       </c>
-      <c r="E68" s="141">
+      <c r="E68" s="114">
         <v>0.03</v>
       </c>
-      <c r="F68" s="141">
+      <c r="F68" s="114">
         <v>-0.03</v>
       </c>
       <c r="G68" s="38" t="s">
@@ -13408,13 +13389,13 @@
       <c r="C69" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D69" s="141">
+      <c r="D69" s="114">
         <v>0.61099999999999999</v>
       </c>
-      <c r="E69" s="141">
+      <c r="E69" s="114">
         <v>0.03</v>
       </c>
-      <c r="F69" s="141">
+      <c r="F69" s="114">
         <v>-0.03</v>
       </c>
       <c r="G69" s="38" t="s">
@@ -13466,13 +13447,13 @@
       <c r="C70" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D70" s="141">
+      <c r="D70" s="114">
         <v>2.2429999999999999</v>
       </c>
-      <c r="E70" s="141">
+      <c r="E70" s="114">
         <v>0.03</v>
       </c>
-      <c r="F70" s="141">
+      <c r="F70" s="114">
         <v>-0.03</v>
       </c>
       <c r="G70" s="38" t="s">
@@ -13524,13 +13505,13 @@
       <c r="C71" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D71" s="141">
+      <c r="D71" s="114">
         <v>2.2429999999999999</v>
       </c>
-      <c r="E71" s="141">
+      <c r="E71" s="114">
         <v>0.03</v>
       </c>
-      <c r="F71" s="141">
+      <c r="F71" s="114">
         <v>-0.03</v>
       </c>
       <c r="G71" s="38" t="s">
@@ -13582,13 +13563,13 @@
       <c r="C72" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D72" s="141">
+      <c r="D72" s="114">
         <v>2.2429999999999999</v>
       </c>
-      <c r="E72" s="141">
+      <c r="E72" s="114">
         <v>0.03</v>
       </c>
-      <c r="F72" s="141">
+      <c r="F72" s="114">
         <v>-0.03</v>
       </c>
       <c r="G72" s="38" t="s">
@@ -13640,13 +13621,13 @@
       <c r="C73" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="D73" s="141">
-        <v>0</v>
-      </c>
-      <c r="E73" s="141">
+      <c r="D73" s="114">
+        <v>0</v>
+      </c>
+      <c r="E73" s="114">
         <v>0.02</v>
       </c>
-      <c r="F73" s="141">
+      <c r="F73" s="114">
         <v>0</v>
       </c>
       <c r="G73" s="38" t="s">
@@ -13698,13 +13679,13 @@
       <c r="C74" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D74" s="141">
+      <c r="D74" s="114">
         <v>3.7559999999999998</v>
       </c>
-      <c r="E74" s="141">
+      <c r="E74" s="114">
         <v>0.02</v>
       </c>
-      <c r="F74" s="141">
+      <c r="F74" s="114">
         <v>-0.02</v>
       </c>
       <c r="G74" s="38" t="s">
@@ -13756,13 +13737,13 @@
       <c r="C75" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D75" s="141">
+      <c r="D75" s="114">
         <v>3.7559999999999998</v>
       </c>
-      <c r="E75" s="141">
+      <c r="E75" s="114">
         <v>0.02</v>
       </c>
-      <c r="F75" s="141">
+      <c r="F75" s="114">
         <v>-0.02</v>
       </c>
       <c r="G75" s="38" t="s">
@@ -13814,13 +13795,13 @@
       <c r="C76" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D76" s="141">
+      <c r="D76" s="114">
         <v>3.7559999999999998</v>
       </c>
-      <c r="E76" s="141">
+      <c r="E76" s="114">
         <v>0.02</v>
       </c>
-      <c r="F76" s="141">
+      <c r="F76" s="114">
         <v>-0.02</v>
       </c>
       <c r="G76" s="38" t="s">
@@ -13872,13 +13853,13 @@
       <c r="C77" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D77" s="141">
+      <c r="D77" s="114">
         <v>0.91</v>
       </c>
-      <c r="E77" s="141">
+      <c r="E77" s="114">
         <v>0.02</v>
       </c>
-      <c r="F77" s="141">
+      <c r="F77" s="114">
         <v>-0.02</v>
       </c>
       <c r="G77" s="38" t="s">
@@ -13930,13 +13911,13 @@
       <c r="C78" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D78" s="141">
+      <c r="D78" s="114">
         <v>0.91</v>
       </c>
-      <c r="E78" s="141">
+      <c r="E78" s="114">
         <v>0.02</v>
       </c>
-      <c r="F78" s="141">
+      <c r="F78" s="114">
         <v>-0.02</v>
       </c>
       <c r="G78" s="38" t="s">
@@ -13988,13 +13969,13 @@
       <c r="C79" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D79" s="141">
+      <c r="D79" s="114">
         <v>0.91</v>
       </c>
-      <c r="E79" s="141">
+      <c r="E79" s="114">
         <v>0.02</v>
       </c>
-      <c r="F79" s="141">
+      <c r="F79" s="114">
         <v>-0.02</v>
       </c>
       <c r="G79" s="38" t="s">
@@ -14046,13 +14027,13 @@
       <c r="C80" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D80" s="141">
+      <c r="D80" s="114">
         <v>6.9059999999999997</v>
       </c>
-      <c r="E80" s="141">
+      <c r="E80" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F80" s="141">
+      <c r="F80" s="114">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="G80" s="38" t="s">
@@ -14104,13 +14085,13 @@
       <c r="C81" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D81" s="141">
+      <c r="D81" s="114">
         <v>6.9059999999999997</v>
       </c>
-      <c r="E81" s="141">
+      <c r="E81" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F81" s="141">
+      <c r="F81" s="114">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="G81" s="38" t="s">
@@ -14162,13 +14143,13 @@
       <c r="C82" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D82" s="141">
+      <c r="D82" s="114">
         <v>6.9059999999999997</v>
       </c>
-      <c r="E82" s="141">
+      <c r="E82" s="114">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F82" s="141">
+      <c r="F82" s="114">
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="G82" s="38" t="s">
@@ -14220,13 +14201,13 @@
       <c r="C83" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D83" s="141">
+      <c r="D83" s="114">
         <v>1.85</v>
       </c>
-      <c r="E83" s="141">
+      <c r="E83" s="114">
         <v>0.02</v>
       </c>
-      <c r="F83" s="141">
+      <c r="F83" s="114">
         <v>-0.02</v>
       </c>
       <c r="G83" s="38" t="s">
@@ -14278,13 +14259,13 @@
       <c r="C84" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D84" s="141">
+      <c r="D84" s="114">
         <v>1.85</v>
       </c>
-      <c r="E84" s="141">
+      <c r="E84" s="114">
         <v>0.02</v>
       </c>
-      <c r="F84" s="141">
+      <c r="F84" s="114">
         <v>-0.02</v>
       </c>
       <c r="G84" s="38" t="s">
@@ -14336,13 +14317,13 @@
       <c r="C85" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D85" s="141">
+      <c r="D85" s="114">
         <v>0.47</v>
       </c>
-      <c r="E85" s="141">
+      <c r="E85" s="114">
         <v>0.01</v>
       </c>
-      <c r="F85" s="141">
+      <c r="F85" s="114">
         <v>-0.03</v>
       </c>
       <c r="G85" s="38" t="s">
@@ -14394,13 +14375,13 @@
       <c r="C86" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D86" s="141">
+      <c r="D86" s="114">
         <v>0.25</v>
       </c>
-      <c r="E86" s="141">
+      <c r="E86" s="114">
         <v>0.01</v>
       </c>
-      <c r="F86" s="141">
+      <c r="F86" s="114">
         <v>-0.03</v>
       </c>
       <c r="G86" s="38" t="s">
@@ -14452,13 +14433,13 @@
       <c r="C87" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D87" s="141">
+      <c r="D87" s="114">
         <v>0.41099999999999998</v>
       </c>
-      <c r="E87" s="141">
+      <c r="E87" s="114">
         <v>0.01</v>
       </c>
-      <c r="F87" s="141">
+      <c r="F87" s="114">
         <v>-0.03</v>
       </c>
       <c r="G87" s="38" t="s">
@@ -14510,13 +14491,13 @@
       <c r="C88" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D88" s="141">
+      <c r="D88" s="114">
         <v>0.41099999999999998</v>
       </c>
-      <c r="E88" s="141">
+      <c r="E88" s="114">
         <v>0.01</v>
       </c>
-      <c r="F88" s="141">
+      <c r="F88" s="114">
         <v>-0.03</v>
       </c>
       <c r="G88" s="38" t="s">
@@ -14568,13 +14549,13 @@
       <c r="C89" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D89" s="141">
+      <c r="D89" s="114">
         <v>0.17</v>
       </c>
-      <c r="E89" s="141">
+      <c r="E89" s="114">
         <v>0.02</v>
       </c>
-      <c r="F89" s="141">
+      <c r="F89" s="114">
         <v>-0.02</v>
       </c>
       <c r="G89" s="38" t="s">
@@ -14626,13 +14607,13 @@
       <c r="C90" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D90" s="141">
+      <c r="D90" s="114">
         <v>0.17</v>
       </c>
-      <c r="E90" s="141">
+      <c r="E90" s="114">
         <v>0.02</v>
       </c>
-      <c r="F90" s="141">
+      <c r="F90" s="114">
         <v>-0.02</v>
       </c>
       <c r="G90" s="38" t="s">
@@ -14684,13 +14665,13 @@
       <c r="C91" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D91" s="141">
+      <c r="D91" s="114">
         <v>0.45500000000000002</v>
       </c>
-      <c r="E91" s="141">
+      <c r="E91" s="114">
         <v>0.02</v>
       </c>
-      <c r="F91" s="141">
+      <c r="F91" s="114">
         <v>-0.02</v>
       </c>
       <c r="G91" s="38" t="s">
@@ -14742,13 +14723,13 @@
       <c r="C92" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D92" s="141">
+      <c r="D92" s="114">
         <v>0.45500000000000002</v>
       </c>
-      <c r="E92" s="141">
+      <c r="E92" s="114">
         <v>0.02</v>
       </c>
-      <c r="F92" s="141">
+      <c r="F92" s="114">
         <v>-0.02</v>
       </c>
       <c r="G92" s="38" t="s">
@@ -14800,13 +14781,13 @@
       <c r="C93" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D93" s="141">
+      <c r="D93" s="114">
         <v>7.9009999999999998</v>
       </c>
-      <c r="E93" s="141">
+      <c r="E93" s="114">
         <v>0.02</v>
       </c>
-      <c r="F93" s="141">
+      <c r="F93" s="114">
         <v>-0.02</v>
       </c>
       <c r="G93" s="38" t="s">
@@ -14858,13 +14839,13 @@
       <c r="C94" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D94" s="141">
+      <c r="D94" s="114">
         <v>11.72</v>
       </c>
-      <c r="E94" s="141">
+      <c r="E94" s="114">
         <v>0.02</v>
       </c>
-      <c r="F94" s="141">
+      <c r="F94" s="114">
         <v>-0.02</v>
       </c>
       <c r="G94" s="38" t="s">
@@ -14916,13 +14897,13 @@
       <c r="C95" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D95" s="141">
+      <c r="D95" s="114">
         <v>11.72</v>
       </c>
-      <c r="E95" s="141">
+      <c r="E95" s="114">
         <v>0.02</v>
       </c>
-      <c r="F95" s="141">
+      <c r="F95" s="114">
         <v>-0.02</v>
       </c>
       <c r="G95" s="38" t="s">
@@ -14974,13 +14955,13 @@
       <c r="C96" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D96" s="141">
+      <c r="D96" s="114">
         <v>0.434</v>
       </c>
-      <c r="E96" s="141">
+      <c r="E96" s="114">
         <v>0.02</v>
       </c>
-      <c r="F96" s="141">
+      <c r="F96" s="114">
         <v>-0.02</v>
       </c>
       <c r="G96" s="38" t="s">
@@ -15032,13 +15013,13 @@
       <c r="C97" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D97" s="141">
+      <c r="D97" s="114">
         <v>0.434</v>
       </c>
-      <c r="E97" s="141">
+      <c r="E97" s="114">
         <v>0.02</v>
       </c>
-      <c r="F97" s="141">
+      <c r="F97" s="114">
         <v>-0.02</v>
       </c>
       <c r="G97" s="38" t="s">
@@ -15090,13 +15071,13 @@
       <c r="C98" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D98" s="141">
+      <c r="D98" s="114">
         <v>3.073</v>
       </c>
-      <c r="E98" s="141">
+      <c r="E98" s="114">
         <v>0.02</v>
       </c>
-      <c r="F98" s="141">
+      <c r="F98" s="114">
         <v>-0.02</v>
       </c>
       <c r="G98" s="38" t="s">
@@ -15148,13 +15129,13 @@
       <c r="C99" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D99" s="141">
+      <c r="D99" s="114">
         <v>1.4610000000000001</v>
       </c>
-      <c r="E99" s="141">
+      <c r="E99" s="114">
         <v>0.02</v>
       </c>
-      <c r="F99" s="141">
+      <c r="F99" s="114">
         <v>-0.02</v>
       </c>
       <c r="G99" s="38" t="s">
@@ -15206,13 +15187,13 @@
       <c r="C100" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D100" s="141">
+      <c r="D100" s="114">
         <v>1.4610000000000001</v>
       </c>
-      <c r="E100" s="141">
+      <c r="E100" s="114">
         <v>0.02</v>
       </c>
-      <c r="F100" s="141">
+      <c r="F100" s="114">
         <v>-0.02</v>
       </c>
       <c r="G100" s="38" t="s">
@@ -15264,13 +15245,13 @@
       <c r="C101" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D101" s="141">
+      <c r="D101" s="114">
         <v>0.42899999999999999</v>
       </c>
-      <c r="E101" s="141">
+      <c r="E101" s="114">
         <v>0.02</v>
       </c>
-      <c r="F101" s="141">
+      <c r="F101" s="114">
         <v>-0.02</v>
       </c>
       <c r="G101" s="38" t="s">
@@ -15322,13 +15303,13 @@
       <c r="C102" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D102" s="141">
+      <c r="D102" s="114">
         <v>0.42899999999999999</v>
       </c>
-      <c r="E102" s="141">
+      <c r="E102" s="114">
         <v>0.02</v>
       </c>
-      <c r="F102" s="141">
+      <c r="F102" s="114">
         <v>-0.02</v>
       </c>
       <c r="G102" s="38" t="s">
@@ -15380,13 +15361,13 @@
       <c r="C103" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D103" s="141">
+      <c r="D103" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E103" s="141">
+      <c r="E103" s="114">
         <v>0.03</v>
       </c>
-      <c r="F103" s="141">
+      <c r="F103" s="114">
         <v>-0.03</v>
       </c>
       <c r="G103" s="38" t="s">
@@ -15438,13 +15419,13 @@
       <c r="C104" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D104" s="141">
+      <c r="D104" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E104" s="141">
+      <c r="E104" s="114">
         <v>0.03</v>
       </c>
-      <c r="F104" s="141">
+      <c r="F104" s="114">
         <v>-0.03</v>
       </c>
       <c r="G104" s="38" t="s">
@@ -15496,13 +15477,13 @@
       <c r="C105" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D105" s="141">
+      <c r="D105" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E105" s="141">
+      <c r="E105" s="114">
         <v>0.03</v>
       </c>
-      <c r="F105" s="141">
+      <c r="F105" s="114">
         <v>-0.03</v>
       </c>
       <c r="G105" s="38" t="s">
@@ -15554,13 +15535,13 @@
       <c r="C106" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D106" s="141">
+      <c r="D106" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E106" s="141">
+      <c r="E106" s="114">
         <v>0.03</v>
       </c>
-      <c r="F106" s="141">
+      <c r="F106" s="114">
         <v>-0.03</v>
       </c>
       <c r="G106" s="38" t="s">
@@ -15612,13 +15593,13 @@
       <c r="C107" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D107" s="141">
+      <c r="D107" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E107" s="141">
+      <c r="E107" s="114">
         <v>0.03</v>
       </c>
-      <c r="F107" s="141">
+      <c r="F107" s="114">
         <v>-0.03</v>
       </c>
       <c r="G107" s="38" t="s">
@@ -15670,13 +15651,13 @@
       <c r="C108" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D108" s="141">
+      <c r="D108" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E108" s="141">
+      <c r="E108" s="114">
         <v>0.03</v>
       </c>
-      <c r="F108" s="141">
+      <c r="F108" s="114">
         <v>-0.03</v>
       </c>
       <c r="G108" s="38" t="s">
@@ -15728,13 +15709,13 @@
       <c r="C109" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D109" s="141">
+      <c r="D109" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E109" s="141">
+      <c r="E109" s="114">
         <v>0.03</v>
       </c>
-      <c r="F109" s="141">
+      <c r="F109" s="114">
         <v>-0.03</v>
       </c>
       <c r="G109" s="38" t="s">
@@ -15786,13 +15767,13 @@
       <c r="C110" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D110" s="141">
+      <c r="D110" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E110" s="141">
+      <c r="E110" s="114">
         <v>0.03</v>
       </c>
-      <c r="F110" s="141">
+      <c r="F110" s="114">
         <v>-0.03</v>
       </c>
       <c r="G110" s="38" t="s">
@@ -15844,13 +15825,13 @@
       <c r="C111" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D111" s="141">
+      <c r="D111" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E111" s="141">
+      <c r="E111" s="114">
         <v>0.03</v>
       </c>
-      <c r="F111" s="141">
+      <c r="F111" s="114">
         <v>-0.03</v>
       </c>
       <c r="G111" s="38" t="s">
@@ -15902,13 +15883,13 @@
       <c r="C112" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D112" s="141">
+      <c r="D112" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E112" s="141">
+      <c r="E112" s="114">
         <v>0.03</v>
       </c>
-      <c r="F112" s="141">
+      <c r="F112" s="114">
         <v>-0.03</v>
       </c>
       <c r="G112" s="38" t="s">
@@ -15960,13 +15941,13 @@
       <c r="C113" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D113" s="141">
+      <c r="D113" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E113" s="141">
+      <c r="E113" s="114">
         <v>0.03</v>
       </c>
-      <c r="F113" s="141">
+      <c r="F113" s="114">
         <v>-0.03</v>
       </c>
       <c r="G113" s="38" t="s">
@@ -16018,13 +15999,13 @@
       <c r="C114" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D114" s="141">
+      <c r="D114" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E114" s="141">
+      <c r="E114" s="114">
         <v>0.03</v>
       </c>
-      <c r="F114" s="141">
+      <c r="F114" s="114">
         <v>-0.03</v>
       </c>
       <c r="G114" s="38" t="s">
@@ -16076,13 +16057,13 @@
       <c r="C115" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D115" s="141">
+      <c r="D115" s="114">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E115" s="141">
+      <c r="E115" s="114">
         <v>0.03</v>
       </c>
-      <c r="F115" s="141">
+      <c r="F115" s="114">
         <v>-0.03</v>
       </c>
       <c r="G115" s="38" t="s">
@@ -16134,13 +16115,13 @@
       <c r="C116" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D116" s="141">
+      <c r="D116" s="114">
         <v>5.157</v>
       </c>
-      <c r="E116" s="141">
+      <c r="E116" s="114">
         <v>0.3</v>
       </c>
-      <c r="F116" s="141">
+      <c r="F116" s="114">
         <v>-0.3</v>
       </c>
       <c r="G116" s="38" t="s">
@@ -16192,13 +16173,13 @@
       <c r="C117" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D117" s="141">
+      <c r="D117" s="114">
         <v>14.095000000000001</v>
       </c>
-      <c r="E117" s="141">
+      <c r="E117" s="114">
         <v>0.17499999999999999</v>
       </c>
-      <c r="F117" s="141">
+      <c r="F117" s="114">
         <v>-0.17499999999999999</v>
       </c>
       <c r="G117" s="38" t="s">
@@ -16250,13 +16231,13 @@
       <c r="C118" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D118" s="141">
+      <c r="D118" s="114">
         <v>0.79</v>
       </c>
-      <c r="E118" s="141">
+      <c r="E118" s="114">
         <v>0.02</v>
       </c>
-      <c r="F118" s="141">
+      <c r="F118" s="114">
         <v>-0.02</v>
       </c>
       <c r="G118" s="38" t="s">
@@ -16308,13 +16289,13 @@
       <c r="C119" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D119" s="141">
+      <c r="D119" s="114">
         <v>0.79</v>
       </c>
-      <c r="E119" s="141">
+      <c r="E119" s="114">
         <v>0.02</v>
       </c>
-      <c r="F119" s="141">
+      <c r="F119" s="114">
         <v>-0.02</v>
       </c>
       <c r="G119" s="38" t="s">
@@ -16366,13 +16347,13 @@
       <c r="C120" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D120" s="141">
+      <c r="D120" s="114">
         <v>0.79</v>
       </c>
-      <c r="E120" s="141">
+      <c r="E120" s="114">
         <v>0.02</v>
       </c>
-      <c r="F120" s="141">
+      <c r="F120" s="114">
         <v>-0.02</v>
       </c>
       <c r="G120" s="38" t="s">
@@ -16424,13 +16405,13 @@
       <c r="C121" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D121" s="141">
+      <c r="D121" s="114">
         <v>0.79</v>
       </c>
-      <c r="E121" s="141">
+      <c r="E121" s="114">
         <v>0.02</v>
       </c>
-      <c r="F121" s="141">
+      <c r="F121" s="114">
         <v>-0.02</v>
       </c>
       <c r="G121" s="38" t="s">
@@ -16482,13 +16463,13 @@
       <c r="C122" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D122" s="141">
+      <c r="D122" s="114">
         <v>0.79</v>
       </c>
-      <c r="E122" s="141">
+      <c r="E122" s="114">
         <v>0.02</v>
       </c>
-      <c r="F122" s="141">
+      <c r="F122" s="114">
         <v>-0.02</v>
       </c>
       <c r="G122" s="38" t="s">
@@ -16540,13 +16521,13 @@
       <c r="C123" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D123" s="141">
+      <c r="D123" s="114">
         <v>0.79</v>
       </c>
-      <c r="E123" s="141">
+      <c r="E123" s="114">
         <v>0.02</v>
       </c>
-      <c r="F123" s="141">
+      <c r="F123" s="114">
         <v>-0.02</v>
       </c>
       <c r="G123" s="38" t="s">
@@ -16598,13 +16579,13 @@
       <c r="C124" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="D124" s="141">
-        <v>0</v>
-      </c>
-      <c r="E124" s="141">
+      <c r="D124" s="114">
+        <v>0</v>
+      </c>
+      <c r="E124" s="114">
         <v>3</v>
       </c>
-      <c r="F124" s="141">
+      <c r="F124" s="114">
         <v>-3</v>
       </c>
       <c r="G124" s="38" t="s">
@@ -16656,13 +16637,13 @@
       <c r="C125" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D125" s="141">
+      <c r="D125" s="114">
         <v>12.99</v>
       </c>
-      <c r="E125" s="141">
+      <c r="E125" s="114">
         <v>0.03</v>
       </c>
-      <c r="F125" s="141">
+      <c r="F125" s="114">
         <v>-0.03</v>
       </c>
       <c r="G125" s="38" t="s">
@@ -16714,13 +16695,13 @@
       <c r="C126" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D126" s="141">
+      <c r="D126" s="114">
         <v>12.750999999999999</v>
       </c>
-      <c r="E126" s="141">
+      <c r="E126" s="114">
         <v>0.03</v>
       </c>
-      <c r="F126" s="141">
+      <c r="F126" s="114">
         <v>-0.03</v>
       </c>
       <c r="G126" s="38" t="s">
@@ -16772,13 +16753,13 @@
       <c r="C127" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D127" s="141">
+      <c r="D127" s="114">
         <v>1.706</v>
       </c>
-      <c r="E127" s="141">
+      <c r="E127" s="114">
         <v>0.03</v>
       </c>
-      <c r="F127" s="141">
+      <c r="F127" s="114">
         <v>-0.03</v>
       </c>
       <c r="G127" s="38" t="s">
@@ -16830,13 +16811,13 @@
       <c r="C128" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="D128" s="141">
-        <v>0</v>
-      </c>
-      <c r="E128" s="141">
+      <c r="D128" s="114">
+        <v>0</v>
+      </c>
+      <c r="E128" s="114">
         <v>0.03</v>
       </c>
-      <c r="F128" s="141">
+      <c r="F128" s="114">
         <v>0</v>
       </c>
       <c r="G128" s="38" t="s">
@@ -16888,13 +16869,13 @@
       <c r="C129" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="D129" s="141">
-        <v>0</v>
-      </c>
-      <c r="E129" s="141">
+      <c r="D129" s="114">
+        <v>0</v>
+      </c>
+      <c r="E129" s="114">
         <v>0.03</v>
       </c>
-      <c r="F129" s="141">
+      <c r="F129" s="114">
         <v>0</v>
       </c>
       <c r="G129" s="38" t="s">
@@ -16946,13 +16927,13 @@
       <c r="C130" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D130" s="141">
-        <v>0</v>
-      </c>
-      <c r="E130" s="141">
+      <c r="D130" s="114">
+        <v>0</v>
+      </c>
+      <c r="E130" s="114">
         <v>0.03</v>
       </c>
-      <c r="F130" s="141">
+      <c r="F130" s="114">
         <v>-0.03</v>
       </c>
       <c r="G130" s="38" t="s">
@@ -17004,13 +16985,13 @@
       <c r="C131" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D131" s="141">
-        <v>0</v>
-      </c>
-      <c r="E131" s="141">
+      <c r="D131" s="114">
+        <v>0</v>
+      </c>
+      <c r="E131" s="114">
         <v>0.03</v>
       </c>
-      <c r="F131" s="141">
+      <c r="F131" s="114">
         <v>-0.03</v>
       </c>
       <c r="G131" s="38" t="s">
@@ -17062,13 +17043,13 @@
       <c r="C132" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D132" s="141">
-        <v>0</v>
-      </c>
-      <c r="E132" s="141">
+      <c r="D132" s="114">
+        <v>0</v>
+      </c>
+      <c r="E132" s="114">
         <v>0.03</v>
       </c>
-      <c r="F132" s="141">
+      <c r="F132" s="114">
         <v>-0.03</v>
       </c>
       <c r="G132" s="38" t="s">
@@ -17120,13 +17101,13 @@
       <c r="C133" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D133" s="141">
-        <v>0</v>
-      </c>
-      <c r="E133" s="141">
+      <c r="D133" s="114">
+        <v>0</v>
+      </c>
+      <c r="E133" s="114">
         <v>0.03</v>
       </c>
-      <c r="F133" s="141">
+      <c r="F133" s="114">
         <v>-0.03</v>
       </c>
       <c r="G133" s="38" t="s">
@@ -17178,13 +17159,13 @@
       <c r="C134" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D134" s="141">
-        <v>0</v>
-      </c>
-      <c r="E134" s="141">
+      <c r="D134" s="114">
+        <v>0</v>
+      </c>
+      <c r="E134" s="114">
         <v>0.03</v>
       </c>
-      <c r="F134" s="141">
+      <c r="F134" s="114">
         <v>-0.03</v>
       </c>
       <c r="G134" s="38" t="s">
@@ -17236,13 +17217,13 @@
       <c r="C135" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D135" s="141">
-        <v>0</v>
-      </c>
-      <c r="E135" s="141">
+      <c r="D135" s="114">
+        <v>0</v>
+      </c>
+      <c r="E135" s="114">
         <v>0.03</v>
       </c>
-      <c r="F135" s="141">
+      <c r="F135" s="114">
         <v>-0.03</v>
       </c>
       <c r="G135" s="38" t="s">
@@ -17294,13 +17275,13 @@
       <c r="C136" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D136" s="141">
-        <v>0</v>
-      </c>
-      <c r="E136" s="141">
+      <c r="D136" s="114">
+        <v>0</v>
+      </c>
+      <c r="E136" s="114">
         <v>0.03</v>
       </c>
-      <c r="F136" s="141">
+      <c r="F136" s="114">
         <v>-0.03</v>
       </c>
       <c r="G136" s="38" t="s">
@@ -17352,13 +17333,13 @@
       <c r="C137" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D137" s="141">
-        <v>0</v>
-      </c>
-      <c r="E137" s="141">
+      <c r="D137" s="114">
+        <v>0</v>
+      </c>
+      <c r="E137" s="114">
         <v>0.03</v>
       </c>
-      <c r="F137" s="141">
+      <c r="F137" s="114">
         <v>-0.03</v>
       </c>
       <c r="G137" s="38" t="s">
@@ -17410,13 +17391,13 @@
       <c r="C138" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D138" s="141">
-        <v>0</v>
-      </c>
-      <c r="E138" s="141">
+      <c r="D138" s="114">
+        <v>0</v>
+      </c>
+      <c r="E138" s="114">
         <v>0.03</v>
       </c>
-      <c r="F138" s="141">
+      <c r="F138" s="114">
         <v>-0.03</v>
       </c>
       <c r="G138" s="38" t="s">
@@ -17468,13 +17449,13 @@
       <c r="C139" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D139" s="141">
-        <v>0</v>
-      </c>
-      <c r="E139" s="141">
+      <c r="D139" s="114">
+        <v>0</v>
+      </c>
+      <c r="E139" s="114">
         <v>0.03</v>
       </c>
-      <c r="F139" s="141">
+      <c r="F139" s="114">
         <v>-0.03</v>
       </c>
       <c r="G139" s="38" t="s">
@@ -17526,13 +17507,13 @@
       <c r="C140" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D140" s="141">
-        <v>0</v>
-      </c>
-      <c r="E140" s="141">
+      <c r="D140" s="114">
+        <v>0</v>
+      </c>
+      <c r="E140" s="114">
         <v>0.03</v>
       </c>
-      <c r="F140" s="141">
+      <c r="F140" s="114">
         <v>-0.03</v>
       </c>
       <c r="G140" s="38" t="s">
@@ -17584,13 +17565,13 @@
       <c r="C141" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D141" s="141">
-        <v>0</v>
-      </c>
-      <c r="E141" s="141">
+      <c r="D141" s="114">
+        <v>0</v>
+      </c>
+      <c r="E141" s="114">
         <v>0.03</v>
       </c>
-      <c r="F141" s="141">
+      <c r="F141" s="114">
         <v>-0.03</v>
       </c>
       <c r="G141" s="38" t="s">
@@ -17642,13 +17623,13 @@
       <c r="C142" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="D142" s="141">
+      <c r="D142" s="114">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="E142" s="141">
+      <c r="E142" s="114">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F142" s="141">
+      <c r="F142" s="114">
         <v>-3.5000000000000003E-2</v>
       </c>
       <c r="G142" s="38" t="s">
@@ -17700,13 +17681,13 @@
       <c r="C143" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="D143" s="141">
+      <c r="D143" s="114">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="E143" s="141">
+      <c r="E143" s="114">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F143" s="141">
+      <c r="F143" s="114">
         <v>-3.5000000000000003E-2</v>
       </c>
       <c r="G143" s="38" t="s">
@@ -17758,13 +17739,13 @@
       <c r="C144" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="D144" s="141">
-        <v>0</v>
-      </c>
-      <c r="E144" s="141">
+      <c r="D144" s="114">
+        <v>0</v>
+      </c>
+      <c r="E144" s="114">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F144" s="141">
+      <c r="F144" s="114">
         <v>0</v>
       </c>
       <c r="G144" s="38" t="s">
@@ -17816,13 +17797,13 @@
       <c r="C145" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="D145" s="141">
-        <v>0</v>
-      </c>
-      <c r="E145" s="141">
+      <c r="D145" s="114">
+        <v>0</v>
+      </c>
+      <c r="E145" s="114">
         <v>0.06</v>
       </c>
-      <c r="F145" s="141">
+      <c r="F145" s="114">
         <v>0</v>
       </c>
       <c r="G145" s="38" t="s">
@@ -17874,13 +17855,13 @@
       <c r="C146" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D146" s="141">
+      <c r="D146" s="114">
         <v>0.8</v>
       </c>
-      <c r="E146" s="141">
+      <c r="E146" s="114">
         <v>0.02</v>
       </c>
-      <c r="F146" s="141">
+      <c r="F146" s="114">
         <v>-0.02</v>
       </c>
       <c r="G146" s="38" t="s">
@@ -17932,13 +17913,13 @@
       <c r="C147" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D147" s="141">
+      <c r="D147" s="114">
         <v>0.8</v>
       </c>
-      <c r="E147" s="141">
+      <c r="E147" s="114">
         <v>0.02</v>
       </c>
-      <c r="F147" s="141">
+      <c r="F147" s="114">
         <v>-0.02</v>
       </c>
       <c r="G147" s="38" t="s">
@@ -17990,13 +17971,13 @@
       <c r="C148" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D148" s="141">
+      <c r="D148" s="114">
         <v>11.807</v>
       </c>
-      <c r="E148" s="141">
+      <c r="E148" s="114">
         <v>0.02</v>
       </c>
-      <c r="F148" s="141">
+      <c r="F148" s="114">
         <v>-0.02</v>
       </c>
       <c r="G148" s="38" t="s">
@@ -18048,13 +18029,13 @@
       <c r="C149" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="D149" s="141">
-        <v>0</v>
-      </c>
-      <c r="E149" s="141">
+      <c r="D149" s="114">
+        <v>0</v>
+      </c>
+      <c r="E149" s="114">
         <v>0.03</v>
       </c>
-      <c r="F149" s="141">
+      <c r="F149" s="114">
         <v>0</v>
       </c>
       <c r="G149" s="38" t="s">
@@ -18106,13 +18087,13 @@
       <c r="C150" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="D150" s="141">
-        <v>0</v>
-      </c>
-      <c r="E150" s="141">
+      <c r="D150" s="114">
+        <v>0</v>
+      </c>
+      <c r="E150" s="114">
         <v>0.03</v>
       </c>
-      <c r="F150" s="141">
+      <c r="F150" s="114">
         <v>0</v>
       </c>
       <c r="G150" s="38" t="s">
@@ -18164,13 +18145,13 @@
       <c r="C151" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="D151" s="141">
-        <v>0</v>
-      </c>
-      <c r="E151" s="141">
+      <c r="D151" s="114">
+        <v>0</v>
+      </c>
+      <c r="E151" s="114">
         <v>0.03</v>
       </c>
-      <c r="F151" s="141">
+      <c r="F151" s="114">
         <v>0</v>
       </c>
       <c r="G151" s="38" t="s">
@@ -18222,13 +18203,13 @@
       <c r="C152" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="D152" s="141">
-        <v>0</v>
-      </c>
-      <c r="E152" s="141">
+      <c r="D152" s="114">
+        <v>0</v>
+      </c>
+      <c r="E152" s="114">
         <v>0.03</v>
       </c>
-      <c r="F152" s="141">
+      <c r="F152" s="114">
         <v>0</v>
       </c>
       <c r="G152" s="38" t="s">
@@ -18311,65 +18292,65 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAB0B3B-EFC8-764F-9B01-BC70951A7277}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:BN98"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="0.81640625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="7.81640625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.77734375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" style="15" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" style="15" customWidth="1"/>
-    <col min="6" max="7" width="8.1796875" style="15" customWidth="1"/>
-    <col min="8" max="8" width="7.81640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" style="15" hidden="1" customWidth="1"/>
-    <col min="10" max="11" width="7.81640625" style="15" customWidth="1"/>
-    <col min="12" max="12" width="0.81640625" style="15" customWidth="1"/>
-    <col min="13" max="16" width="7.81640625" style="15" customWidth="1"/>
-    <col min="17" max="22" width="7.81640625" style="15" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="7.81640625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="15" customWidth="1"/>
+    <col min="6" max="7" width="8.21875" style="15" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="15" customWidth="1"/>
+    <col min="9" max="9" width="7.77734375" style="15" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="7.77734375" style="15" customWidth="1"/>
+    <col min="12" max="12" width="0.77734375" style="15" customWidth="1"/>
+    <col min="13" max="16" width="7.77734375" style="15" customWidth="1"/>
+    <col min="17" max="22" width="7.77734375" style="15" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="7.77734375" style="15" customWidth="1"/>
     <col min="24" max="24" width="10" style="15" hidden="1" customWidth="1"/>
-    <col min="25" max="27" width="9.453125" style="15" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="7.81640625" style="15" customWidth="1"/>
+    <col min="25" max="27" width="9.44140625" style="15" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="7.77734375" style="15" customWidth="1"/>
     <col min="29" max="29" width="9" style="15" customWidth="1"/>
-    <col min="30" max="30" width="8.6328125" style="15" customWidth="1"/>
+    <col min="30" max="30" width="8.6640625" style="15" customWidth="1"/>
     <col min="31" max="32" width="9" style="15" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="7.54296875" style="15" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="0.81640625" style="15" customWidth="1"/>
-    <col min="35" max="66" width="7.81640625" style="95" customWidth="1"/>
-    <col min="67" max="16384" width="8.81640625" style="95"/>
+    <col min="33" max="33" width="7.5546875" style="15" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="0.77734375" style="15" customWidth="1"/>
+    <col min="35" max="66" width="7.77734375" style="95" customWidth="1"/>
+    <col min="67" max="16384" width="8.77734375" style="95"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" s="21" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A1" s="119" t="s">
+    <row r="1" spans="1:66" s="21" customFormat="1" ht="22.15" customHeight="1">
+      <c r="A1" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="123"/>
+      <c r="T1" s="123"/>
+      <c r="U1" s="123"/>
+      <c r="V1" s="123"/>
+      <c r="W1" s="123"/>
+      <c r="X1" s="123"/>
+      <c r="Y1" s="123"/>
+      <c r="Z1" s="123"/>
+      <c r="AA1" s="123"/>
+      <c r="AB1" s="123"/>
+      <c r="AC1" s="123"/>
       <c r="AD1" s="20"/>
       <c r="AE1" s="20"/>
       <c r="AF1" s="20"/>
@@ -18414,81 +18395,81 @@
     </row>
     <row r="3" spans="1:66" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="46"/>
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="126" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="123"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="127"/>
       <c r="L3" s="47"/>
-      <c r="M3" s="122" t="s">
+      <c r="M3" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="N3" s="121"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="121"/>
-      <c r="Q3" s="121"/>
-      <c r="R3" s="121"/>
-      <c r="S3" s="121"/>
-      <c r="T3" s="121"/>
-      <c r="U3" s="121"/>
-      <c r="V3" s="121"/>
-      <c r="W3" s="121"/>
-      <c r="X3" s="121"/>
-      <c r="Y3" s="121"/>
-      <c r="Z3" s="121"/>
-      <c r="AA3" s="121"/>
-      <c r="AB3" s="121"/>
-      <c r="AC3" s="123"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="125"/>
+      <c r="W3" s="125"/>
+      <c r="X3" s="125"/>
+      <c r="Y3" s="125"/>
+      <c r="Z3" s="125"/>
+      <c r="AA3" s="125"/>
+      <c r="AB3" s="125"/>
+      <c r="AC3" s="127"/>
       <c r="AD3" s="48"/>
-      <c r="AE3" s="138" t="s">
+      <c r="AE3" s="142" t="s">
         <v>54</v>
       </c>
-      <c r="AF3" s="138"/>
-      <c r="AG3" s="138"/>
+      <c r="AF3" s="142"/>
+      <c r="AG3" s="142"/>
       <c r="AH3" s="22"/>
-      <c r="AI3" s="132" t="s">
+      <c r="AI3" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="AJ3" s="133"/>
-      <c r="AK3" s="133"/>
-      <c r="AL3" s="133"/>
-      <c r="AM3" s="133"/>
-      <c r="AN3" s="133"/>
-      <c r="AO3" s="133"/>
-      <c r="AP3" s="133"/>
-      <c r="AQ3" s="133"/>
-      <c r="AR3" s="133"/>
-      <c r="AS3" s="133"/>
-      <c r="AT3" s="133"/>
-      <c r="AU3" s="133"/>
-      <c r="AV3" s="133"/>
-      <c r="AW3" s="133"/>
-      <c r="AX3" s="133"/>
-      <c r="AY3" s="133"/>
-      <c r="AZ3" s="133"/>
-      <c r="BA3" s="133"/>
-      <c r="BB3" s="133"/>
-      <c r="BC3" s="133"/>
-      <c r="BD3" s="133"/>
-      <c r="BE3" s="133"/>
-      <c r="BF3" s="133"/>
-      <c r="BG3" s="133"/>
-      <c r="BH3" s="133"/>
-      <c r="BI3" s="133"/>
-      <c r="BJ3" s="133"/>
-      <c r="BK3" s="133"/>
-      <c r="BL3" s="133"/>
-      <c r="BM3" s="133"/>
-      <c r="BN3" s="134"/>
+      <c r="AJ3" s="137"/>
+      <c r="AK3" s="137"/>
+      <c r="AL3" s="137"/>
+      <c r="AM3" s="137"/>
+      <c r="AN3" s="137"/>
+      <c r="AO3" s="137"/>
+      <c r="AP3" s="137"/>
+      <c r="AQ3" s="137"/>
+      <c r="AR3" s="137"/>
+      <c r="AS3" s="137"/>
+      <c r="AT3" s="137"/>
+      <c r="AU3" s="137"/>
+      <c r="AV3" s="137"/>
+      <c r="AW3" s="137"/>
+      <c r="AX3" s="137"/>
+      <c r="AY3" s="137"/>
+      <c r="AZ3" s="137"/>
+      <c r="BA3" s="137"/>
+      <c r="BB3" s="137"/>
+      <c r="BC3" s="137"/>
+      <c r="BD3" s="137"/>
+      <c r="BE3" s="137"/>
+      <c r="BF3" s="137"/>
+      <c r="BG3" s="137"/>
+      <c r="BH3" s="137"/>
+      <c r="BI3" s="137"/>
+      <c r="BJ3" s="137"/>
+      <c r="BK3" s="137"/>
+      <c r="BL3" s="137"/>
+      <c r="BM3" s="137"/>
+      <c r="BN3" s="138"/>
     </row>
-    <row r="4" spans="1:66" s="23" customFormat="1" ht="25.2" customHeight="1">
+    <row r="4" spans="1:66" s="23" customFormat="1" ht="25.15" customHeight="1">
       <c r="A4" s="46"/>
       <c r="B4" s="49"/>
       <c r="C4" s="49"/>
@@ -18516,10 +18497,10 @@
       <c r="U4" s="56"/>
       <c r="V4" s="56"/>
       <c r="W4" s="56"/>
-      <c r="X4" s="139" t="s">
+      <c r="X4" s="143" t="s">
         <v>58</v>
       </c>
-      <c r="Y4" s="140"/>
+      <c r="Y4" s="144"/>
       <c r="Z4" s="57" t="s">
         <v>59</v>
       </c>
@@ -18533,40 +18514,40 @@
       <c r="AF4" s="22"/>
       <c r="AG4" s="60"/>
       <c r="AH4" s="61"/>
-      <c r="AI4" s="135"/>
-      <c r="AJ4" s="136"/>
-      <c r="AK4" s="136"/>
-      <c r="AL4" s="136"/>
-      <c r="AM4" s="136"/>
-      <c r="AN4" s="136"/>
-      <c r="AO4" s="136"/>
-      <c r="AP4" s="136"/>
-      <c r="AQ4" s="136"/>
-      <c r="AR4" s="136"/>
-      <c r="AS4" s="136"/>
-      <c r="AT4" s="136"/>
-      <c r="AU4" s="136"/>
-      <c r="AV4" s="136"/>
-      <c r="AW4" s="136"/>
-      <c r="AX4" s="136"/>
-      <c r="AY4" s="136"/>
-      <c r="AZ4" s="136"/>
-      <c r="BA4" s="136"/>
-      <c r="BB4" s="136"/>
-      <c r="BC4" s="136"/>
-      <c r="BD4" s="136"/>
-      <c r="BE4" s="136"/>
-      <c r="BF4" s="136"/>
-      <c r="BG4" s="136"/>
-      <c r="BH4" s="136"/>
-      <c r="BI4" s="136"/>
-      <c r="BJ4" s="136"/>
-      <c r="BK4" s="136"/>
-      <c r="BL4" s="136"/>
-      <c r="BM4" s="136"/>
-      <c r="BN4" s="137"/>
+      <c r="AI4" s="139"/>
+      <c r="AJ4" s="140"/>
+      <c r="AK4" s="140"/>
+      <c r="AL4" s="140"/>
+      <c r="AM4" s="140"/>
+      <c r="AN4" s="140"/>
+      <c r="AO4" s="140"/>
+      <c r="AP4" s="140"/>
+      <c r="AQ4" s="140"/>
+      <c r="AR4" s="140"/>
+      <c r="AS4" s="140"/>
+      <c r="AT4" s="140"/>
+      <c r="AU4" s="140"/>
+      <c r="AV4" s="140"/>
+      <c r="AW4" s="140"/>
+      <c r="AX4" s="140"/>
+      <c r="AY4" s="140"/>
+      <c r="AZ4" s="140"/>
+      <c r="BA4" s="140"/>
+      <c r="BB4" s="140"/>
+      <c r="BC4" s="140"/>
+      <c r="BD4" s="140"/>
+      <c r="BE4" s="140"/>
+      <c r="BF4" s="140"/>
+      <c r="BG4" s="140"/>
+      <c r="BH4" s="140"/>
+      <c r="BI4" s="140"/>
+      <c r="BJ4" s="140"/>
+      <c r="BK4" s="140"/>
+      <c r="BL4" s="140"/>
+      <c r="BM4" s="140"/>
+      <c r="BN4" s="141"/>
     </row>
-    <row r="5" spans="1:66" s="76" customFormat="1" ht="22.8">
+    <row r="5" spans="1:66" s="76" customFormat="1" ht="24">
       <c r="A5" s="62"/>
       <c r="B5" s="63" t="s">
         <v>60</v>
@@ -18690,7 +18671,7 @@
       <c r="BM5" s="75"/>
       <c r="BN5" s="75"/>
     </row>
-    <row r="6" spans="1:66" ht="19.2" customHeight="1">
+    <row r="6" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B6" s="77" t="s">
         <v>84</v>
       </c>
@@ -18700,16 +18681,16 @@
       <c r="D6" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="142">
+      <c r="E6" s="115">
         <v>0.5</v>
       </c>
-      <c r="F6" s="143">
+      <c r="F6" s="116">
         <v>0.01</v>
       </c>
-      <c r="G6" s="143">
+      <c r="G6" s="116">
         <v>-0.01</v>
       </c>
-      <c r="H6" s="144" t="s">
+      <c r="H6" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I6" s="79" t="s">
@@ -18826,7 +18807,7 @@
       <c r="BM6" s="94"/>
       <c r="BN6" s="94"/>
     </row>
-    <row r="7" spans="1:66" ht="19.2" customHeight="1">
+    <row r="7" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B7" s="77" t="s">
         <v>84</v>
       </c>
@@ -18836,16 +18817,16 @@
       <c r="D7" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="142">
+      <c r="E7" s="115">
         <v>0.5</v>
       </c>
-      <c r="F7" s="143">
+      <c r="F7" s="116">
         <v>0.01</v>
       </c>
-      <c r="G7" s="143">
+      <c r="G7" s="116">
         <v>-0.01</v>
       </c>
-      <c r="H7" s="144" t="s">
+      <c r="H7" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I7" s="79" t="s">
@@ -18962,7 +18943,7 @@
       <c r="BM7" s="94"/>
       <c r="BN7" s="94"/>
     </row>
-    <row r="8" spans="1:66" ht="19.2" customHeight="1">
+    <row r="8" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B8" s="77" t="s">
         <v>84</v>
       </c>
@@ -18972,16 +18953,16 @@
       <c r="D8" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="142">
+      <c r="E8" s="115">
         <v>0.5</v>
       </c>
-      <c r="F8" s="143">
+      <c r="F8" s="116">
         <v>0.01</v>
       </c>
-      <c r="G8" s="143">
+      <c r="G8" s="116">
         <v>-0.01</v>
       </c>
-      <c r="H8" s="144" t="s">
+      <c r="H8" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I8" s="79" t="s">
@@ -19098,7 +19079,7 @@
       <c r="BM8" s="94"/>
       <c r="BN8" s="94"/>
     </row>
-    <row r="9" spans="1:66" ht="19.2" customHeight="1">
+    <row r="9" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B9" s="77" t="s">
         <v>86</v>
       </c>
@@ -19108,16 +19089,16 @@
       <c r="D9" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="142">
-        <v>0</v>
-      </c>
-      <c r="F9" s="143">
+      <c r="E9" s="115">
+        <v>0</v>
+      </c>
+      <c r="F9" s="116">
         <v>0.02</v>
       </c>
-      <c r="G9" s="143">
-        <v>0</v>
-      </c>
-      <c r="H9" s="144" t="s">
+      <c r="G9" s="116">
+        <v>0</v>
+      </c>
+      <c r="H9" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I9" s="79" t="s">
@@ -19234,7 +19215,7 @@
       <c r="BM9" s="94"/>
       <c r="BN9" s="94"/>
     </row>
-    <row r="10" spans="1:66" ht="19.2" customHeight="1">
+    <row r="10" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B10" s="77" t="s">
         <v>87</v>
       </c>
@@ -19244,16 +19225,16 @@
       <c r="D10" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="142">
-        <v>0</v>
-      </c>
-      <c r="F10" s="143">
+      <c r="E10" s="115">
+        <v>0</v>
+      </c>
+      <c r="F10" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G10" s="143">
-        <v>0</v>
-      </c>
-      <c r="H10" s="144" t="s">
+      <c r="G10" s="116">
+        <v>0</v>
+      </c>
+      <c r="H10" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I10" s="79" t="s">
@@ -19370,7 +19351,7 @@
       <c r="BM10" s="94"/>
       <c r="BN10" s="94"/>
     </row>
-    <row r="11" spans="1:66" ht="19.2" customHeight="1">
+    <row r="11" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B11" s="77" t="s">
         <v>88</v>
       </c>
@@ -19380,16 +19361,16 @@
       <c r="D11" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="142">
-        <v>0</v>
-      </c>
-      <c r="F11" s="143">
+      <c r="E11" s="115">
+        <v>0</v>
+      </c>
+      <c r="F11" s="116">
         <v>0.02</v>
       </c>
-      <c r="G11" s="143">
-        <v>0</v>
-      </c>
-      <c r="H11" s="144" t="s">
+      <c r="G11" s="116">
+        <v>0</v>
+      </c>
+      <c r="H11" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I11" s="79" t="s">
@@ -19506,7 +19487,7 @@
       <c r="BM11" s="94"/>
       <c r="BN11" s="94"/>
     </row>
-    <row r="12" spans="1:66" ht="19.2" customHeight="1">
+    <row r="12" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B12" s="77" t="s">
         <v>89</v>
       </c>
@@ -19516,16 +19497,16 @@
       <c r="D12" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="142">
+      <c r="E12" s="115">
         <v>12.612</v>
       </c>
-      <c r="F12" s="143">
+      <c r="F12" s="116">
         <v>0.02</v>
       </c>
-      <c r="G12" s="143">
+      <c r="G12" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H12" s="144" t="s">
+      <c r="H12" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="79" t="s">
@@ -19642,7 +19623,7 @@
       <c r="BM12" s="94"/>
       <c r="BN12" s="94"/>
     </row>
-    <row r="13" spans="1:66" ht="19.2" customHeight="1">
+    <row r="13" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B13" s="77" t="s">
         <v>90</v>
       </c>
@@ -19652,16 +19633,16 @@
       <c r="D13" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="142">
+      <c r="E13" s="115">
         <v>0.04</v>
       </c>
-      <c r="F13" s="143">
+      <c r="F13" s="116">
         <v>0.02</v>
       </c>
-      <c r="G13" s="143">
+      <c r="G13" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H13" s="144" t="s">
+      <c r="H13" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I13" s="79" t="s">
@@ -19778,7 +19759,7 @@
       <c r="BM13" s="94"/>
       <c r="BN13" s="94"/>
     </row>
-    <row r="14" spans="1:66" ht="19.2" customHeight="1">
+    <row r="14" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B14" s="77" t="s">
         <v>90</v>
       </c>
@@ -19788,16 +19769,16 @@
       <c r="D14" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="142">
+      <c r="E14" s="115">
         <v>0.04</v>
       </c>
-      <c r="F14" s="143">
+      <c r="F14" s="116">
         <v>0.02</v>
       </c>
-      <c r="G14" s="143">
+      <c r="G14" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H14" s="144" t="s">
+      <c r="H14" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I14" s="79" t="s">
@@ -19914,7 +19895,7 @@
       <c r="BM14" s="94"/>
       <c r="BN14" s="94"/>
     </row>
-    <row r="15" spans="1:66" ht="19.2" customHeight="1">
+    <row r="15" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B15" s="77" t="s">
         <v>91</v>
       </c>
@@ -19924,16 +19905,16 @@
       <c r="D15" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="142">
+      <c r="E15" s="115">
         <v>12.382</v>
       </c>
-      <c r="F15" s="143">
+      <c r="F15" s="116">
         <v>0.02</v>
       </c>
-      <c r="G15" s="143">
+      <c r="G15" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H15" s="144" t="s">
+      <c r="H15" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I15" s="79" t="s">
@@ -20050,7 +20031,7 @@
       <c r="BM15" s="94"/>
       <c r="BN15" s="94"/>
     </row>
-    <row r="16" spans="1:66" ht="19.2" customHeight="1">
+    <row r="16" spans="1:66" ht="19.149999999999999" customHeight="1">
       <c r="B16" s="77" t="s">
         <v>92</v>
       </c>
@@ -20060,16 +20041,16 @@
       <c r="D16" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="142">
+      <c r="E16" s="115">
         <v>14.726000000000001</v>
       </c>
-      <c r="F16" s="143">
+      <c r="F16" s="116">
         <v>0.02</v>
       </c>
-      <c r="G16" s="143">
+      <c r="G16" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H16" s="144" t="s">
+      <c r="H16" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I16" s="79" t="s">
@@ -20186,7 +20167,7 @@
       <c r="BM16" s="94"/>
       <c r="BN16" s="94"/>
     </row>
-    <row r="17" spans="2:66" ht="19.2" customHeight="1">
+    <row r="17" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B17" s="77" t="s">
         <v>93</v>
       </c>
@@ -20196,16 +20177,16 @@
       <c r="D17" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="142">
+      <c r="E17" s="115">
         <v>14.506</v>
       </c>
-      <c r="F17" s="143">
+      <c r="F17" s="116">
         <v>0.02</v>
       </c>
-      <c r="G17" s="143">
+      <c r="G17" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H17" s="144" t="s">
+      <c r="H17" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I17" s="79" t="s">
@@ -20322,7 +20303,7 @@
       <c r="BM17" s="94"/>
       <c r="BN17" s="94"/>
     </row>
-    <row r="18" spans="2:66" ht="19.2" customHeight="1">
+    <row r="18" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B18" s="77" t="s">
         <v>94</v>
       </c>
@@ -20332,16 +20313,16 @@
       <c r="D18" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="142">
+      <c r="E18" s="115">
         <v>0.05</v>
       </c>
-      <c r="F18" s="143">
+      <c r="F18" s="116">
         <v>0.02</v>
       </c>
-      <c r="G18" s="143">
+      <c r="G18" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H18" s="144" t="s">
+      <c r="H18" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I18" s="79" t="s">
@@ -20458,7 +20439,7 @@
       <c r="BM18" s="94"/>
       <c r="BN18" s="94"/>
     </row>
-    <row r="19" spans="2:66" ht="19.2" customHeight="1">
+    <row r="19" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B19" s="77" t="s">
         <v>94</v>
       </c>
@@ -20468,16 +20449,16 @@
       <c r="D19" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="142">
+      <c r="E19" s="115">
         <v>0.05</v>
       </c>
-      <c r="F19" s="143">
+      <c r="F19" s="116">
         <v>0.02</v>
       </c>
-      <c r="G19" s="143">
+      <c r="G19" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H19" s="144" t="s">
+      <c r="H19" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I19" s="79"/>
@@ -20592,7 +20573,7 @@
       <c r="BM19" s="94"/>
       <c r="BN19" s="94"/>
     </row>
-    <row r="20" spans="2:66" ht="19.2" customHeight="1">
+    <row r="20" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B20" s="77" t="s">
         <v>95</v>
       </c>
@@ -20602,16 +20583,16 @@
       <c r="D20" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="142">
+      <c r="E20" s="115">
         <v>9.9190000000000005</v>
       </c>
-      <c r="F20" s="143">
+      <c r="F20" s="116">
         <v>0.02</v>
       </c>
-      <c r="G20" s="143">
+      <c r="G20" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H20" s="144" t="s">
+      <c r="H20" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I20" s="79"/>
@@ -20726,7 +20707,7 @@
       <c r="BM20" s="94"/>
       <c r="BN20" s="94"/>
     </row>
-    <row r="21" spans="2:66" ht="19.2" customHeight="1">
+    <row r="21" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B21" s="77" t="s">
         <v>95</v>
       </c>
@@ -20736,16 +20717,16 @@
       <c r="D21" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="142">
+      <c r="E21" s="115">
         <v>9.9190000000000005</v>
       </c>
-      <c r="F21" s="143">
+      <c r="F21" s="116">
         <v>0.02</v>
       </c>
-      <c r="G21" s="143">
+      <c r="G21" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H21" s="144" t="s">
+      <c r="H21" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I21" s="79"/>
@@ -20860,7 +20841,7 @@
       <c r="BM21" s="94"/>
       <c r="BN21" s="94"/>
     </row>
-    <row r="22" spans="2:66" ht="19.2" customHeight="1">
+    <row r="22" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B22" s="77" t="s">
         <v>95</v>
       </c>
@@ -20870,16 +20851,16 @@
       <c r="D22" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="142">
+      <c r="E22" s="115">
         <v>9.9190000000000005</v>
       </c>
-      <c r="F22" s="143">
+      <c r="F22" s="116">
         <v>0.02</v>
       </c>
-      <c r="G22" s="143">
+      <c r="G22" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H22" s="144" t="s">
+      <c r="H22" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I22" s="79"/>
@@ -20994,7 +20975,7 @@
       <c r="BM22" s="94"/>
       <c r="BN22" s="94"/>
     </row>
-    <row r="23" spans="2:66" ht="19.2" customHeight="1">
+    <row r="23" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B23" s="77" t="s">
         <v>96</v>
       </c>
@@ -21004,16 +20985,16 @@
       <c r="D23" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="142">
+      <c r="E23" s="115">
         <v>12.795</v>
       </c>
-      <c r="F23" s="143">
+      <c r="F23" s="116">
         <v>0.02</v>
       </c>
-      <c r="G23" s="143">
+      <c r="G23" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H23" s="144" t="s">
+      <c r="H23" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="79"/>
@@ -21128,7 +21109,7 @@
       <c r="BM23" s="94"/>
       <c r="BN23" s="94"/>
     </row>
-    <row r="24" spans="2:66" ht="19.2" customHeight="1">
+    <row r="24" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B24" s="77" t="s">
         <v>96</v>
       </c>
@@ -21138,16 +21119,16 @@
       <c r="D24" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="142">
+      <c r="E24" s="115">
         <v>12.795</v>
       </c>
-      <c r="F24" s="143">
+      <c r="F24" s="116">
         <v>0.02</v>
       </c>
-      <c r="G24" s="143">
+      <c r="G24" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H24" s="144" t="s">
+      <c r="H24" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I24" s="79"/>
@@ -21262,7 +21243,7 @@
       <c r="BM24" s="94"/>
       <c r="BN24" s="94"/>
     </row>
-    <row r="25" spans="2:66" ht="19.2" customHeight="1">
+    <row r="25" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B25" s="77" t="s">
         <v>96</v>
       </c>
@@ -21272,16 +21253,16 @@
       <c r="D25" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="142">
+      <c r="E25" s="115">
         <v>12.795</v>
       </c>
-      <c r="F25" s="143">
+      <c r="F25" s="116">
         <v>0.02</v>
       </c>
-      <c r="G25" s="143">
+      <c r="G25" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H25" s="144" t="s">
+      <c r="H25" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I25" s="79"/>
@@ -21384,7 +21365,7 @@
       <c r="BM25" s="94"/>
       <c r="BN25" s="94"/>
     </row>
-    <row r="26" spans="2:66" ht="19.2" customHeight="1">
+    <row r="26" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B26" s="77" t="s">
         <v>97</v>
       </c>
@@ -21394,16 +21375,16 @@
       <c r="D26" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="142">
+      <c r="E26" s="115">
         <v>0.105</v>
       </c>
-      <c r="F26" s="143">
+      <c r="F26" s="116">
         <v>0.02</v>
       </c>
-      <c r="G26" s="143">
+      <c r="G26" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H26" s="144" t="s">
+      <c r="H26" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I26" s="79"/>
@@ -21506,7 +21487,7 @@
       <c r="BM26" s="94"/>
       <c r="BN26" s="94"/>
     </row>
-    <row r="27" spans="2:66" ht="19.2" customHeight="1">
+    <row r="27" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B27" s="77" t="s">
         <v>97</v>
       </c>
@@ -21516,16 +21497,16 @@
       <c r="D27" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="142">
+      <c r="E27" s="115">
         <v>0.105</v>
       </c>
-      <c r="F27" s="143">
+      <c r="F27" s="116">
         <v>0.02</v>
       </c>
-      <c r="G27" s="143">
+      <c r="G27" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H27" s="144" t="s">
+      <c r="H27" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I27" s="79"/>
@@ -21628,7 +21609,7 @@
       <c r="BM27" s="94"/>
       <c r="BN27" s="94"/>
     </row>
-    <row r="28" spans="2:66" ht="19.2" customHeight="1">
+    <row r="28" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B28" s="77" t="s">
         <v>98</v>
       </c>
@@ -21638,16 +21619,16 @@
       <c r="D28" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="142">
+      <c r="E28" s="115">
         <v>0.91</v>
       </c>
-      <c r="F28" s="143">
+      <c r="F28" s="116">
         <v>0.02</v>
       </c>
-      <c r="G28" s="143">
+      <c r="G28" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H28" s="144" t="s">
+      <c r="H28" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I28" s="79"/>
@@ -21750,7 +21731,7 @@
       <c r="BM28" s="94"/>
       <c r="BN28" s="94"/>
     </row>
-    <row r="29" spans="2:66" ht="19.2" customHeight="1">
+    <row r="29" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B29" s="77" t="s">
         <v>98</v>
       </c>
@@ -21760,16 +21741,16 @@
       <c r="D29" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="142">
+      <c r="E29" s="115">
         <v>0.91</v>
       </c>
-      <c r="F29" s="143">
+      <c r="F29" s="116">
         <v>0.02</v>
       </c>
-      <c r="G29" s="143">
+      <c r="G29" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H29" s="144" t="s">
+      <c r="H29" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I29" s="79"/>
@@ -21872,7 +21853,7 @@
       <c r="BM29" s="94"/>
       <c r="BN29" s="94"/>
     </row>
-    <row r="30" spans="2:66" ht="19.2" customHeight="1">
+    <row r="30" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B30" s="77" t="s">
         <v>98</v>
       </c>
@@ -21882,16 +21863,16 @@
       <c r="D30" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="142">
+      <c r="E30" s="115">
         <v>0.91</v>
       </c>
-      <c r="F30" s="143">
+      <c r="F30" s="116">
         <v>0.02</v>
       </c>
-      <c r="G30" s="143">
+      <c r="G30" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H30" s="144" t="s">
+      <c r="H30" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I30" s="79"/>
@@ -22006,7 +21987,7 @@
       <c r="BM30" s="94"/>
       <c r="BN30" s="94"/>
     </row>
-    <row r="31" spans="2:66" ht="19.2" customHeight="1">
+    <row r="31" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B31" s="77" t="s">
         <v>99</v>
       </c>
@@ -22016,16 +21997,16 @@
       <c r="D31" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="142">
+      <c r="E31" s="115">
         <v>0.86</v>
       </c>
-      <c r="F31" s="143">
+      <c r="F31" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G31" s="143">
+      <c r="G31" s="116">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H31" s="144" t="s">
+      <c r="H31" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I31" s="79"/>
@@ -22140,7 +22121,7 @@
       <c r="BM31" s="94"/>
       <c r="BN31" s="94"/>
     </row>
-    <row r="32" spans="2:66" ht="19.2" customHeight="1">
+    <row r="32" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B32" s="77" t="s">
         <v>99</v>
       </c>
@@ -22150,16 +22131,16 @@
       <c r="D32" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="142">
+      <c r="E32" s="115">
         <v>0.86</v>
       </c>
-      <c r="F32" s="143">
+      <c r="F32" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G32" s="143">
+      <c r="G32" s="116">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H32" s="144" t="s">
+      <c r="H32" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I32" s="79"/>
@@ -22274,7 +22255,7 @@
       <c r="BM32" s="94"/>
       <c r="BN32" s="94"/>
     </row>
-    <row r="33" spans="2:66" ht="19.2" customHeight="1">
+    <row r="33" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B33" s="77" t="s">
         <v>99</v>
       </c>
@@ -22284,16 +22265,16 @@
       <c r="D33" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="142">
+      <c r="E33" s="115">
         <v>0.86</v>
       </c>
-      <c r="F33" s="143">
+      <c r="F33" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G33" s="143">
+      <c r="G33" s="116">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H33" s="144" t="s">
+      <c r="H33" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I33" s="79"/>
@@ -22408,7 +22389,7 @@
       <c r="BM33" s="94"/>
       <c r="BN33" s="94"/>
     </row>
-    <row r="34" spans="2:66" ht="19.2" customHeight="1">
+    <row r="34" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B34" s="77" t="s">
         <v>100</v>
       </c>
@@ -22418,16 +22399,16 @@
       <c r="D34" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="142">
+      <c r="E34" s="115">
         <v>0.87</v>
       </c>
-      <c r="F34" s="143">
+      <c r="F34" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G34" s="143">
+      <c r="G34" s="116">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H34" s="144" t="s">
+      <c r="H34" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I34" s="79"/>
@@ -22542,7 +22523,7 @@
       <c r="BM34" s="94"/>
       <c r="BN34" s="94"/>
     </row>
-    <row r="35" spans="2:66" ht="19.2" customHeight="1">
+    <row r="35" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B35" s="77" t="s">
         <v>100</v>
       </c>
@@ -22552,16 +22533,16 @@
       <c r="D35" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E35" s="142">
+      <c r="E35" s="115">
         <v>0.87</v>
       </c>
-      <c r="F35" s="143">
+      <c r="F35" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G35" s="143">
+      <c r="G35" s="116">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H35" s="144" t="s">
+      <c r="H35" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I35" s="79"/>
@@ -22676,7 +22657,7 @@
       <c r="BM35" s="94"/>
       <c r="BN35" s="94"/>
     </row>
-    <row r="36" spans="2:66" ht="19.2" customHeight="1">
+    <row r="36" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B36" s="77" t="s">
         <v>101</v>
       </c>
@@ -22686,16 +22667,16 @@
       <c r="D36" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E36" s="142">
+      <c r="E36" s="115">
         <v>12.561999999999999</v>
       </c>
-      <c r="F36" s="143">
+      <c r="F36" s="116">
         <v>0.02</v>
       </c>
-      <c r="G36" s="143">
+      <c r="G36" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H36" s="144" t="s">
+      <c r="H36" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I36" s="79"/>
@@ -22810,7 +22791,7 @@
       <c r="BM36" s="94"/>
       <c r="BN36" s="94"/>
     </row>
-    <row r="37" spans="2:66" ht="19.2" customHeight="1">
+    <row r="37" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B37" s="77" t="s">
         <v>102</v>
       </c>
@@ -22820,16 +22801,16 @@
       <c r="D37" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E37" s="142">
+      <c r="E37" s="115">
         <v>12.332000000000001</v>
       </c>
-      <c r="F37" s="143">
+      <c r="F37" s="116">
         <v>0.02</v>
       </c>
-      <c r="G37" s="143">
+      <c r="G37" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H37" s="144" t="s">
+      <c r="H37" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I37" s="79"/>
@@ -22944,7 +22925,7 @@
       <c r="BM37" s="94"/>
       <c r="BN37" s="94"/>
     </row>
-    <row r="38" spans="2:66" ht="19.2" customHeight="1">
+    <row r="38" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B38" s="77" t="s">
         <v>103</v>
       </c>
@@ -22954,16 +22935,16 @@
       <c r="D38" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E38" s="142">
+      <c r="E38" s="115">
         <v>0.35499999999999998</v>
       </c>
-      <c r="F38" s="143">
+      <c r="F38" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G38" s="143">
+      <c r="G38" s="116">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H38" s="144" t="s">
+      <c r="H38" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I38" s="79"/>
@@ -23078,7 +23059,7 @@
       <c r="BM38" s="94"/>
       <c r="BN38" s="94"/>
     </row>
-    <row r="39" spans="2:66" ht="19.2" customHeight="1">
+    <row r="39" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B39" s="77" t="s">
         <v>103</v>
       </c>
@@ -23088,16 +23069,16 @@
       <c r="D39" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="142">
+      <c r="E39" s="115">
         <v>0.35499999999999998</v>
       </c>
-      <c r="F39" s="143">
+      <c r="F39" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G39" s="143">
+      <c r="G39" s="116">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H39" s="144" t="s">
+      <c r="H39" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I39" s="79"/>
@@ -23212,7 +23193,7 @@
       <c r="BM39" s="94"/>
       <c r="BN39" s="94"/>
     </row>
-    <row r="40" spans="2:66" ht="19.2" customHeight="1">
+    <row r="40" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B40" s="77" t="s">
         <v>103</v>
       </c>
@@ -23222,16 +23203,16 @@
       <c r="D40" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="142">
+      <c r="E40" s="115">
         <v>0.35499999999999998</v>
       </c>
-      <c r="F40" s="143">
+      <c r="F40" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G40" s="143">
+      <c r="G40" s="116">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H40" s="144" t="s">
+      <c r="H40" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I40" s="79"/>
@@ -23346,7 +23327,7 @@
       <c r="BM40" s="94"/>
       <c r="BN40" s="94"/>
     </row>
-    <row r="41" spans="2:66" ht="19.2" customHeight="1">
+    <row r="41" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B41" s="77" t="s">
         <v>103</v>
       </c>
@@ -23356,16 +23337,16 @@
       <c r="D41" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E41" s="142">
+      <c r="E41" s="115">
         <v>0.35499999999999998</v>
       </c>
-      <c r="F41" s="143">
+      <c r="F41" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G41" s="143">
+      <c r="G41" s="116">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H41" s="144" t="s">
+      <c r="H41" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I41" s="79"/>
@@ -23480,7 +23461,7 @@
       <c r="BM41" s="94"/>
       <c r="BN41" s="94"/>
     </row>
-    <row r="42" spans="2:66" ht="19.2" customHeight="1">
+    <row r="42" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B42" s="77" t="s">
         <v>104</v>
       </c>
@@ -23490,16 +23471,16 @@
       <c r="D42" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E42" s="142">
+      <c r="E42" s="115">
         <v>0.96299999999999997</v>
       </c>
-      <c r="F42" s="143">
+      <c r="F42" s="116">
         <v>0.02</v>
       </c>
-      <c r="G42" s="143">
+      <c r="G42" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H42" s="144" t="s">
+      <c r="H42" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I42" s="79"/>
@@ -23614,7 +23595,7 @@
       <c r="BM42" s="94"/>
       <c r="BN42" s="94"/>
     </row>
-    <row r="43" spans="2:66" ht="19.2" customHeight="1">
+    <row r="43" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B43" s="77" t="s">
         <v>105</v>
       </c>
@@ -23624,16 +23605,16 @@
       <c r="D43" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E43" s="142">
+      <c r="E43" s="115">
         <v>1.58</v>
       </c>
-      <c r="F43" s="143">
+      <c r="F43" s="116">
         <v>0.02</v>
       </c>
-      <c r="G43" s="143">
+      <c r="G43" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H43" s="144" t="s">
+      <c r="H43" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I43" s="79"/>
@@ -23748,7 +23729,7 @@
       <c r="BM43" s="94"/>
       <c r="BN43" s="94"/>
     </row>
-    <row r="44" spans="2:66" ht="19.2" customHeight="1">
+    <row r="44" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B44" s="77" t="s">
         <v>106</v>
       </c>
@@ -23758,16 +23739,16 @@
       <c r="D44" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E44" s="142">
+      <c r="E44" s="115">
         <v>6.9009999999999998</v>
       </c>
-      <c r="F44" s="143">
+      <c r="F44" s="116">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G44" s="143">
+      <c r="G44" s="116">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="H44" s="144" t="s">
+      <c r="H44" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I44" s="79"/>
@@ -23882,7 +23863,7 @@
       <c r="BM44" s="94"/>
       <c r="BN44" s="94"/>
     </row>
-    <row r="45" spans="2:66" ht="19.2" customHeight="1">
+    <row r="45" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B45" s="77" t="s">
         <v>106</v>
       </c>
@@ -23892,16 +23873,16 @@
       <c r="D45" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E45" s="142">
+      <c r="E45" s="115">
         <v>6.9009999999999998</v>
       </c>
-      <c r="F45" s="143">
+      <c r="F45" s="116">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G45" s="143">
+      <c r="G45" s="116">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="H45" s="144" t="s">
+      <c r="H45" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I45" s="79"/>
@@ -24016,7 +23997,7 @@
       <c r="BM45" s="94"/>
       <c r="BN45" s="94"/>
     </row>
-    <row r="46" spans="2:66" ht="19.2" customHeight="1">
+    <row r="46" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B46" s="77" t="s">
         <v>106</v>
       </c>
@@ -24026,16 +24007,16 @@
       <c r="D46" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E46" s="142">
+      <c r="E46" s="115">
         <v>6.9009999999999998</v>
       </c>
-      <c r="F46" s="143">
+      <c r="F46" s="116">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G46" s="143">
+      <c r="G46" s="116">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="H46" s="144" t="s">
+      <c r="H46" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I46" s="79"/>
@@ -24150,7 +24131,7 @@
       <c r="BM46" s="94"/>
       <c r="BN46" s="94"/>
     </row>
-    <row r="47" spans="2:66" ht="19.2" customHeight="1">
+    <row r="47" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B47" s="77" t="s">
         <v>233</v>
       </c>
@@ -24160,16 +24141,16 @@
       <c r="D47" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E47" s="142">
+      <c r="E47" s="115">
         <v>7.8010000000000002</v>
       </c>
-      <c r="F47" s="143">
+      <c r="F47" s="116">
         <v>0.03</v>
       </c>
-      <c r="G47" s="143">
+      <c r="G47" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H47" s="144" t="s">
+      <c r="H47" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I47" s="79"/>
@@ -24284,7 +24265,7 @@
       <c r="BM47" s="94"/>
       <c r="BN47" s="94"/>
     </row>
-    <row r="48" spans="2:66" ht="19.2" customHeight="1">
+    <row r="48" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B48" s="77" t="s">
         <v>233</v>
       </c>
@@ -24294,16 +24275,16 @@
       <c r="D48" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E48" s="142">
+      <c r="E48" s="115">
         <v>7.8010000000000002</v>
       </c>
-      <c r="F48" s="143">
+      <c r="F48" s="116">
         <v>0.03</v>
       </c>
-      <c r="G48" s="143">
+      <c r="G48" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H48" s="144" t="s">
+      <c r="H48" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I48" s="79"/>
@@ -24418,7 +24399,7 @@
       <c r="BM48" s="94"/>
       <c r="BN48" s="94"/>
     </row>
-    <row r="49" spans="2:66" ht="19.2" customHeight="1">
+    <row r="49" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B49" s="77" t="s">
         <v>233</v>
       </c>
@@ -24428,16 +24409,16 @@
       <c r="D49" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E49" s="142">
+      <c r="E49" s="115">
         <v>7.8010000000000002</v>
       </c>
-      <c r="F49" s="143">
+      <c r="F49" s="116">
         <v>0.03</v>
       </c>
-      <c r="G49" s="143">
+      <c r="G49" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H49" s="144" t="s">
+      <c r="H49" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I49" s="79"/>
@@ -24552,7 +24533,7 @@
       <c r="BM49" s="94"/>
       <c r="BN49" s="94"/>
     </row>
-    <row r="50" spans="2:66" ht="19.2" customHeight="1">
+    <row r="50" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B50" s="77" t="s">
         <v>234</v>
       </c>
@@ -24562,16 +24543,16 @@
       <c r="D50" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E50" s="142">
+      <c r="E50" s="115">
         <v>10.154999999999999</v>
       </c>
-      <c r="F50" s="143">
+      <c r="F50" s="116">
         <v>0.03</v>
       </c>
-      <c r="G50" s="143">
+      <c r="G50" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H50" s="144" t="s">
+      <c r="H50" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I50" s="79"/>
@@ -24686,7 +24667,7 @@
       <c r="BM50" s="94"/>
       <c r="BN50" s="94"/>
     </row>
-    <row r="51" spans="2:66" ht="19.2" customHeight="1">
+    <row r="51" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B51" s="77" t="s">
         <v>234</v>
       </c>
@@ -24696,16 +24677,16 @@
       <c r="D51" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E51" s="142">
+      <c r="E51" s="115">
         <v>10.154999999999999</v>
       </c>
-      <c r="F51" s="143">
+      <c r="F51" s="116">
         <v>0.03</v>
       </c>
-      <c r="G51" s="143">
+      <c r="G51" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H51" s="144" t="s">
+      <c r="H51" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I51" s="79"/>
@@ -24820,7 +24801,7 @@
       <c r="BM51" s="94"/>
       <c r="BN51" s="94"/>
     </row>
-    <row r="52" spans="2:66" ht="19.2" customHeight="1">
+    <row r="52" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B52" s="77" t="s">
         <v>235</v>
       </c>
@@ -24830,16 +24811,16 @@
       <c r="D52" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E52" s="142">
+      <c r="E52" s="115">
         <v>0.626</v>
       </c>
-      <c r="F52" s="143">
+      <c r="F52" s="116">
         <v>0.02</v>
       </c>
-      <c r="G52" s="143">
+      <c r="G52" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H52" s="144" t="s">
+      <c r="H52" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I52" s="79"/>
@@ -24954,7 +24935,7 @@
       <c r="BM52" s="94"/>
       <c r="BN52" s="94"/>
     </row>
-    <row r="53" spans="2:66" ht="19.2" customHeight="1">
+    <row r="53" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B53" s="77" t="s">
         <v>235</v>
       </c>
@@ -24964,16 +24945,16 @@
       <c r="D53" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E53" s="142">
+      <c r="E53" s="115">
         <v>0.626</v>
       </c>
-      <c r="F53" s="143">
+      <c r="F53" s="116">
         <v>0.02</v>
       </c>
-      <c r="G53" s="143">
+      <c r="G53" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H53" s="144" t="s">
+      <c r="H53" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I53" s="79"/>
@@ -25088,7 +25069,7 @@
       <c r="BM53" s="94"/>
       <c r="BN53" s="94"/>
     </row>
-    <row r="54" spans="2:66" ht="19.2" customHeight="1">
+    <row r="54" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B54" s="77" t="s">
         <v>236</v>
       </c>
@@ -25098,16 +25079,16 @@
       <c r="D54" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E54" s="142">
+      <c r="E54" s="115">
         <v>1.9530000000000001</v>
       </c>
-      <c r="F54" s="143">
+      <c r="F54" s="116">
         <v>0.03</v>
       </c>
-      <c r="G54" s="143">
+      <c r="G54" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H54" s="144" t="s">
+      <c r="H54" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I54" s="79"/>
@@ -25222,7 +25203,7 @@
       <c r="BM54" s="94"/>
       <c r="BN54" s="94"/>
     </row>
-    <row r="55" spans="2:66" ht="19.2" customHeight="1">
+    <row r="55" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B55" s="77" t="s">
         <v>236</v>
       </c>
@@ -25232,16 +25213,16 @@
       <c r="D55" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E55" s="142">
+      <c r="E55" s="115">
         <v>1.9530000000000001</v>
       </c>
-      <c r="F55" s="143">
+      <c r="F55" s="116">
         <v>0.03</v>
       </c>
-      <c r="G55" s="143">
+      <c r="G55" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H55" s="144" t="s">
+      <c r="H55" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I55" s="79"/>
@@ -25356,7 +25337,7 @@
       <c r="BM55" s="94"/>
       <c r="BN55" s="94"/>
     </row>
-    <row r="56" spans="2:66" ht="19.2" customHeight="1">
+    <row r="56" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B56" s="77" t="s">
         <v>237</v>
       </c>
@@ -25366,16 +25347,16 @@
       <c r="D56" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E56" s="142">
+      <c r="E56" s="115">
         <v>2.2429999999999999</v>
       </c>
-      <c r="F56" s="143">
+      <c r="F56" s="116">
         <v>0.03</v>
       </c>
-      <c r="G56" s="143">
+      <c r="G56" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H56" s="144" t="s">
+      <c r="H56" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I56" s="79"/>
@@ -25490,7 +25471,7 @@
       <c r="BM56" s="94"/>
       <c r="BN56" s="94"/>
     </row>
-    <row r="57" spans="2:66" ht="19.2" customHeight="1">
+    <row r="57" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B57" s="77" t="s">
         <v>237</v>
       </c>
@@ -25500,16 +25481,16 @@
       <c r="D57" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E57" s="142">
+      <c r="E57" s="115">
         <v>2.2429999999999999</v>
       </c>
-      <c r="F57" s="143">
+      <c r="F57" s="116">
         <v>0.03</v>
       </c>
-      <c r="G57" s="143">
+      <c r="G57" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H57" s="144" t="s">
+      <c r="H57" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I57" s="79"/>
@@ -25624,7 +25605,7 @@
       <c r="BM57" s="94"/>
       <c r="BN57" s="94"/>
     </row>
-    <row r="58" spans="2:66" ht="19.2" customHeight="1">
+    <row r="58" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B58" s="77" t="s">
         <v>237</v>
       </c>
@@ -25634,16 +25615,16 @@
       <c r="D58" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E58" s="142">
+      <c r="E58" s="115">
         <v>2.2429999999999999</v>
       </c>
-      <c r="F58" s="143">
+      <c r="F58" s="116">
         <v>0.03</v>
       </c>
-      <c r="G58" s="143">
+      <c r="G58" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H58" s="144" t="s">
+      <c r="H58" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I58" s="79"/>
@@ -25758,7 +25739,7 @@
       <c r="BM58" s="94"/>
       <c r="BN58" s="94"/>
     </row>
-    <row r="59" spans="2:66" ht="19.2" customHeight="1">
+    <row r="59" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B59" s="77" t="s">
         <v>107</v>
       </c>
@@ -25768,16 +25749,16 @@
       <c r="D59" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E59" s="142">
+      <c r="E59" s="115">
         <v>6.9059999999999997</v>
       </c>
-      <c r="F59" s="143">
+      <c r="F59" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G59" s="143">
+      <c r="G59" s="116">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="H59" s="144" t="s">
+      <c r="H59" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I59" s="79"/>
@@ -25892,7 +25873,7 @@
       <c r="BM59" s="94"/>
       <c r="BN59" s="94"/>
     </row>
-    <row r="60" spans="2:66" ht="19.2" customHeight="1">
+    <row r="60" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B60" s="77" t="s">
         <v>107</v>
       </c>
@@ -25902,16 +25883,16 @@
       <c r="D60" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E60" s="142">
+      <c r="E60" s="115">
         <v>6.9059999999999997</v>
       </c>
-      <c r="F60" s="143">
+      <c r="F60" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G60" s="143">
+      <c r="G60" s="116">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="H60" s="144" t="s">
+      <c r="H60" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I60" s="79"/>
@@ -26026,7 +26007,7 @@
       <c r="BM60" s="94"/>
       <c r="BN60" s="94"/>
     </row>
-    <row r="61" spans="2:66" ht="19.2" customHeight="1">
+    <row r="61" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B61" s="77" t="s">
         <v>107</v>
       </c>
@@ -26036,16 +26017,16 @@
       <c r="D61" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E61" s="142">
+      <c r="E61" s="115">
         <v>6.9059999999999997</v>
       </c>
-      <c r="F61" s="143">
+      <c r="F61" s="116">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G61" s="143">
+      <c r="G61" s="116">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="H61" s="144" t="s">
+      <c r="H61" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I61" s="79"/>
@@ -26160,7 +26141,7 @@
       <c r="BM61" s="94"/>
       <c r="BN61" s="94"/>
     </row>
-    <row r="62" spans="2:66" ht="19.2" customHeight="1">
+    <row r="62" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B62" s="77" t="s">
         <v>108</v>
       </c>
@@ -26170,16 +26151,16 @@
       <c r="D62" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E62" s="142">
+      <c r="E62" s="115">
         <v>0.47</v>
       </c>
-      <c r="F62" s="143">
+      <c r="F62" s="116">
         <v>0.01</v>
       </c>
-      <c r="G62" s="143">
+      <c r="G62" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H62" s="144" t="s">
+      <c r="H62" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I62" s="79"/>
@@ -26294,7 +26275,7 @@
       <c r="BM62" s="94"/>
       <c r="BN62" s="94"/>
     </row>
-    <row r="63" spans="2:66" ht="19.2" customHeight="1">
+    <row r="63" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B63" s="90" t="s">
         <v>109</v>
       </c>
@@ -26304,16 +26285,16 @@
       <c r="D63" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E63" s="142">
+      <c r="E63" s="115">
         <v>0.25</v>
       </c>
-      <c r="F63" s="143">
+      <c r="F63" s="116">
         <v>0.01</v>
       </c>
-      <c r="G63" s="143">
+      <c r="G63" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H63" s="144" t="s">
+      <c r="H63" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I63" s="79"/>
@@ -26428,7 +26409,7 @@
       <c r="BM63" s="94"/>
       <c r="BN63" s="94"/>
     </row>
-    <row r="64" spans="2:66" ht="19.2" customHeight="1">
+    <row r="64" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B64" s="77" t="s">
         <v>110</v>
       </c>
@@ -26438,16 +26419,16 @@
       <c r="D64" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E64" s="142">
+      <c r="E64" s="115">
         <v>0.41099999999999998</v>
       </c>
-      <c r="F64" s="143">
+      <c r="F64" s="116">
         <v>0.01</v>
       </c>
-      <c r="G64" s="143">
+      <c r="G64" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H64" s="144" t="s">
+      <c r="H64" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I64" s="79"/>
@@ -26562,7 +26543,7 @@
       <c r="BM64" s="94"/>
       <c r="BN64" s="94"/>
     </row>
-    <row r="65" spans="2:66" ht="19.2" customHeight="1">
+    <row r="65" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B65" s="77" t="s">
         <v>110</v>
       </c>
@@ -26572,16 +26553,16 @@
       <c r="D65" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E65" s="142">
+      <c r="E65" s="115">
         <v>0.41099999999999998</v>
       </c>
-      <c r="F65" s="143">
+      <c r="F65" s="116">
         <v>0.01</v>
       </c>
-      <c r="G65" s="143">
+      <c r="G65" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H65" s="144" t="s">
+      <c r="H65" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I65" s="79"/>
@@ -26696,7 +26677,7 @@
       <c r="BM65" s="94"/>
       <c r="BN65" s="94"/>
     </row>
-    <row r="66" spans="2:66" ht="19.2" customHeight="1">
+    <row r="66" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B66" s="77" t="s">
         <v>111</v>
       </c>
@@ -26706,16 +26687,16 @@
       <c r="D66" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E66" s="142">
+      <c r="E66" s="115">
         <v>0.17</v>
       </c>
-      <c r="F66" s="143">
+      <c r="F66" s="116">
         <v>0.02</v>
       </c>
-      <c r="G66" s="143">
+      <c r="G66" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H66" s="144" t="s">
+      <c r="H66" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I66" s="79"/>
@@ -26830,7 +26811,7 @@
       <c r="BM66" s="94"/>
       <c r="BN66" s="94"/>
     </row>
-    <row r="67" spans="2:66" ht="19.2" customHeight="1">
+    <row r="67" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B67" s="77" t="s">
         <v>111</v>
       </c>
@@ -26840,16 +26821,16 @@
       <c r="D67" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E67" s="142">
+      <c r="E67" s="115">
         <v>0.17</v>
       </c>
-      <c r="F67" s="143">
+      <c r="F67" s="116">
         <v>0.02</v>
       </c>
-      <c r="G67" s="143">
+      <c r="G67" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H67" s="144" t="s">
+      <c r="H67" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I67" s="79"/>
@@ -26964,7 +26945,7 @@
       <c r="BM67" s="94"/>
       <c r="BN67" s="94"/>
     </row>
-    <row r="68" spans="2:66" ht="19.2" customHeight="1">
+    <row r="68" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B68" s="77" t="s">
         <v>112</v>
       </c>
@@ -26974,16 +26955,16 @@
       <c r="D68" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E68" s="142">
+      <c r="E68" s="115">
         <v>1.4610000000000001</v>
       </c>
-      <c r="F68" s="143">
+      <c r="F68" s="116">
         <v>0.02</v>
       </c>
-      <c r="G68" s="143">
+      <c r="G68" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H68" s="144" t="s">
+      <c r="H68" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I68" s="79"/>
@@ -27098,7 +27079,7 @@
       <c r="BM68" s="94"/>
       <c r="BN68" s="94"/>
     </row>
-    <row r="69" spans="2:66" ht="19.2" customHeight="1">
+    <row r="69" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B69" s="77" t="s">
         <v>112</v>
       </c>
@@ -27108,16 +27089,16 @@
       <c r="D69" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E69" s="142">
+      <c r="E69" s="115">
         <v>1.4610000000000001</v>
       </c>
-      <c r="F69" s="143">
+      <c r="F69" s="116">
         <v>0.02</v>
       </c>
-      <c r="G69" s="143">
+      <c r="G69" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H69" s="144" t="s">
+      <c r="H69" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I69" s="79"/>
@@ -27232,7 +27213,7 @@
       <c r="BM69" s="94"/>
       <c r="BN69" s="94"/>
     </row>
-    <row r="70" spans="2:66" ht="19.2" customHeight="1">
+    <row r="70" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B70" s="77" t="s">
         <v>113</v>
       </c>
@@ -27242,16 +27223,16 @@
       <c r="D70" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E70" s="142">
+      <c r="E70" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F70" s="143">
+      <c r="F70" s="116">
         <v>0.03</v>
       </c>
-      <c r="G70" s="143">
+      <c r="G70" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H70" s="144" t="s">
+      <c r="H70" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I70" s="79"/>
@@ -27366,7 +27347,7 @@
       <c r="BM70" s="94"/>
       <c r="BN70" s="94"/>
     </row>
-    <row r="71" spans="2:66" ht="19.2" customHeight="1">
+    <row r="71" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B71" s="77" t="s">
         <v>113</v>
       </c>
@@ -27376,16 +27357,16 @@
       <c r="D71" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E71" s="142">
+      <c r="E71" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F71" s="143">
+      <c r="F71" s="116">
         <v>0.03</v>
       </c>
-      <c r="G71" s="143">
+      <c r="G71" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H71" s="144" t="s">
+      <c r="H71" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I71" s="79"/>
@@ -27500,7 +27481,7 @@
       <c r="BM71" s="94"/>
       <c r="BN71" s="94"/>
     </row>
-    <row r="72" spans="2:66" ht="19.2" customHeight="1">
+    <row r="72" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B72" s="90" t="s">
         <v>113</v>
       </c>
@@ -27510,16 +27491,16 @@
       <c r="D72" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E72" s="142">
+      <c r="E72" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F72" s="143">
+      <c r="F72" s="116">
         <v>0.03</v>
       </c>
-      <c r="G72" s="143">
+      <c r="G72" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H72" s="144" t="s">
+      <c r="H72" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I72" s="79"/>
@@ -27634,7 +27615,7 @@
       <c r="BM72" s="94"/>
       <c r="BN72" s="94"/>
     </row>
-    <row r="73" spans="2:66" ht="19.2" customHeight="1">
+    <row r="73" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B73" s="90" t="s">
         <v>113</v>
       </c>
@@ -27644,16 +27625,16 @@
       <c r="D73" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E73" s="142">
+      <c r="E73" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F73" s="143">
+      <c r="F73" s="116">
         <v>0.03</v>
       </c>
-      <c r="G73" s="143">
+      <c r="G73" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H73" s="144" t="s">
+      <c r="H73" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I73" s="79"/>
@@ -27768,7 +27749,7 @@
       <c r="BM73" s="94"/>
       <c r="BN73" s="94"/>
     </row>
-    <row r="74" spans="2:66" ht="19.2" customHeight="1">
+    <row r="74" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B74" s="90" t="s">
         <v>113</v>
       </c>
@@ -27778,16 +27759,16 @@
       <c r="D74" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E74" s="142">
+      <c r="E74" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F74" s="143">
+      <c r="F74" s="116">
         <v>0.03</v>
       </c>
-      <c r="G74" s="143">
+      <c r="G74" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H74" s="144" t="s">
+      <c r="H74" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I74" s="79"/>
@@ -27902,7 +27883,7 @@
       <c r="BM74" s="94"/>
       <c r="BN74" s="94"/>
     </row>
-    <row r="75" spans="2:66" ht="19.2" customHeight="1">
+    <row r="75" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B75" s="90" t="s">
         <v>113</v>
       </c>
@@ -27912,16 +27893,16 @@
       <c r="D75" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E75" s="142">
+      <c r="E75" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F75" s="143">
+      <c r="F75" s="116">
         <v>0.03</v>
       </c>
-      <c r="G75" s="143">
+      <c r="G75" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H75" s="144" t="s">
+      <c r="H75" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I75" s="79"/>
@@ -28036,7 +28017,7 @@
       <c r="BM75" s="94"/>
       <c r="BN75" s="94"/>
     </row>
-    <row r="76" spans="2:66" ht="19.2" customHeight="1">
+    <row r="76" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B76" s="90" t="s">
         <v>113</v>
       </c>
@@ -28046,16 +28027,16 @@
       <c r="D76" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E76" s="142">
+      <c r="E76" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F76" s="143">
+      <c r="F76" s="116">
         <v>0.03</v>
       </c>
-      <c r="G76" s="143">
+      <c r="G76" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H76" s="144" t="s">
+      <c r="H76" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I76" s="79"/>
@@ -28170,7 +28151,7 @@
       <c r="BM76" s="94"/>
       <c r="BN76" s="94"/>
     </row>
-    <row r="77" spans="2:66" ht="19.2" customHeight="1">
+    <row r="77" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B77" s="77" t="s">
         <v>113</v>
       </c>
@@ -28180,16 +28161,16 @@
       <c r="D77" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E77" s="142">
+      <c r="E77" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F77" s="143">
+      <c r="F77" s="116">
         <v>0.03</v>
       </c>
-      <c r="G77" s="143">
+      <c r="G77" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H77" s="144" t="s">
+      <c r="H77" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I77" s="79"/>
@@ -28304,7 +28285,7 @@
       <c r="BM77" s="94"/>
       <c r="BN77" s="94"/>
     </row>
-    <row r="78" spans="2:66" ht="19.2" customHeight="1">
+    <row r="78" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B78" s="77" t="s">
         <v>113</v>
       </c>
@@ -28314,16 +28295,16 @@
       <c r="D78" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E78" s="142">
+      <c r="E78" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F78" s="143">
+      <c r="F78" s="116">
         <v>0.03</v>
       </c>
-      <c r="G78" s="143">
+      <c r="G78" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H78" s="144" t="s">
+      <c r="H78" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I78" s="79"/>
@@ -28438,7 +28419,7 @@
       <c r="BM78" s="94"/>
       <c r="BN78" s="94"/>
     </row>
-    <row r="79" spans="2:66" ht="19.2" customHeight="1">
+    <row r="79" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B79" s="77" t="s">
         <v>113</v>
       </c>
@@ -28448,16 +28429,16 @@
       <c r="D79" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E79" s="142">
+      <c r="E79" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F79" s="143">
+      <c r="F79" s="116">
         <v>0.03</v>
       </c>
-      <c r="G79" s="143">
+      <c r="G79" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H79" s="144" t="s">
+      <c r="H79" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I79" s="79"/>
@@ -28572,7 +28553,7 @@
       <c r="BM79" s="94"/>
       <c r="BN79" s="94"/>
     </row>
-    <row r="80" spans="2:66" ht="19.2" customHeight="1">
+    <row r="80" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B80" s="77" t="s">
         <v>113</v>
       </c>
@@ -28582,16 +28563,16 @@
       <c r="D80" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E80" s="142">
+      <c r="E80" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F80" s="143">
+      <c r="F80" s="116">
         <v>0.03</v>
       </c>
-      <c r="G80" s="143">
+      <c r="G80" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H80" s="144" t="s">
+      <c r="H80" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I80" s="79"/>
@@ -28706,7 +28687,7 @@
       <c r="BM80" s="94"/>
       <c r="BN80" s="94"/>
     </row>
-    <row r="81" spans="2:66" ht="19.2" customHeight="1">
+    <row r="81" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B81" s="77" t="s">
         <v>113</v>
       </c>
@@ -28716,16 +28697,16 @@
       <c r="D81" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E81" s="142">
+      <c r="E81" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F81" s="143">
+      <c r="F81" s="116">
         <v>0.03</v>
       </c>
-      <c r="G81" s="143">
+      <c r="G81" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H81" s="144" t="s">
+      <c r="H81" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I81" s="79"/>
@@ -28840,7 +28821,7 @@
       <c r="BM81" s="94"/>
       <c r="BN81" s="94"/>
     </row>
-    <row r="82" spans="2:66" ht="19.2" customHeight="1">
+    <row r="82" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B82" s="77" t="s">
         <v>113</v>
       </c>
@@ -28850,16 +28831,16 @@
       <c r="D82" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E82" s="142">
+      <c r="E82" s="115">
         <v>0.39200000000000002</v>
       </c>
-      <c r="F82" s="143">
+      <c r="F82" s="116">
         <v>0.03</v>
       </c>
-      <c r="G82" s="143">
+      <c r="G82" s="116">
         <v>-0.03</v>
       </c>
-      <c r="H82" s="144" t="s">
+      <c r="H82" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I82" s="79"/>
@@ -28974,7 +28955,7 @@
       <c r="BM82" s="94"/>
       <c r="BN82" s="94"/>
     </row>
-    <row r="83" spans="2:66" ht="19.2" customHeight="1">
+    <row r="83" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B83" s="77" t="s">
         <v>114</v>
       </c>
@@ -28984,16 +28965,16 @@
       <c r="D83" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E83" s="142">
+      <c r="E83" s="115">
         <v>0.79</v>
       </c>
-      <c r="F83" s="143">
+      <c r="F83" s="116">
         <v>0.02</v>
       </c>
-      <c r="G83" s="143">
+      <c r="G83" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H83" s="144" t="s">
+      <c r="H83" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I83" s="79"/>
@@ -29108,7 +29089,7 @@
       <c r="BM83" s="94"/>
       <c r="BN83" s="94"/>
     </row>
-    <row r="84" spans="2:66" ht="19.2" customHeight="1">
+    <row r="84" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B84" s="77" t="s">
         <v>114</v>
       </c>
@@ -29118,16 +29099,16 @@
       <c r="D84" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E84" s="142">
+      <c r="E84" s="115">
         <v>0.79</v>
       </c>
-      <c r="F84" s="143">
+      <c r="F84" s="116">
         <v>0.02</v>
       </c>
-      <c r="G84" s="143">
+      <c r="G84" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H84" s="144" t="s">
+      <c r="H84" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I84" s="79"/>
@@ -29242,7 +29223,7 @@
       <c r="BM84" s="94"/>
       <c r="BN84" s="94"/>
     </row>
-    <row r="85" spans="2:66" ht="19.2" customHeight="1">
+    <row r="85" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B85" s="77" t="s">
         <v>114</v>
       </c>
@@ -29252,16 +29233,16 @@
       <c r="D85" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E85" s="142">
+      <c r="E85" s="115">
         <v>0.79</v>
       </c>
-      <c r="F85" s="143">
+      <c r="F85" s="116">
         <v>0.02</v>
       </c>
-      <c r="G85" s="143">
+      <c r="G85" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H85" s="144" t="s">
+      <c r="H85" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I85" s="79"/>
@@ -29376,7 +29357,7 @@
       <c r="BM85" s="94"/>
       <c r="BN85" s="94"/>
     </row>
-    <row r="86" spans="2:66" ht="19.2" customHeight="1">
+    <row r="86" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B86" s="77" t="s">
         <v>115</v>
       </c>
@@ -29386,16 +29367,16 @@
       <c r="D86" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E86" s="142">
+      <c r="E86" s="115">
         <v>0.79</v>
       </c>
-      <c r="F86" s="143">
+      <c r="F86" s="116">
         <v>0.02</v>
       </c>
-      <c r="G86" s="143">
+      <c r="G86" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H86" s="144" t="s">
+      <c r="H86" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I86" s="79"/>
@@ -29510,7 +29491,7 @@
       <c r="BM86" s="94"/>
       <c r="BN86" s="94"/>
     </row>
-    <row r="87" spans="2:66" ht="19.2" customHeight="1">
+    <row r="87" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B87" s="77" t="s">
         <v>115</v>
       </c>
@@ -29520,16 +29501,16 @@
       <c r="D87" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E87" s="142">
+      <c r="E87" s="115">
         <v>0.79</v>
       </c>
-      <c r="F87" s="143">
+      <c r="F87" s="116">
         <v>0.02</v>
       </c>
-      <c r="G87" s="143">
+      <c r="G87" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H87" s="144" t="s">
+      <c r="H87" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I87" s="79"/>
@@ -29644,7 +29625,7 @@
       <c r="BM87" s="94"/>
       <c r="BN87" s="94"/>
     </row>
-    <row r="88" spans="2:66" ht="19.2" customHeight="1">
+    <row r="88" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B88" s="77" t="s">
         <v>115</v>
       </c>
@@ -29654,16 +29635,16 @@
       <c r="D88" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E88" s="142">
+      <c r="E88" s="115">
         <v>0.79</v>
       </c>
-      <c r="F88" s="143">
+      <c r="F88" s="116">
         <v>0.02</v>
       </c>
-      <c r="G88" s="143">
+      <c r="G88" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H88" s="144" t="s">
+      <c r="H88" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I88" s="79"/>
@@ -29778,7 +29759,7 @@
       <c r="BM88" s="94"/>
       <c r="BN88" s="94"/>
     </row>
-    <row r="89" spans="2:66" ht="19.2" customHeight="1">
+    <row r="89" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B89" s="90" t="s">
         <v>228</v>
       </c>
@@ -29788,16 +29769,16 @@
       <c r="D89" s="78" t="s">
         <v>226</v>
       </c>
-      <c r="E89" s="142">
+      <c r="E89" s="115">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="F89" s="143">
+      <c r="F89" s="116">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G89" s="143">
+      <c r="G89" s="116">
         <v>-3.5000000000000003E-2</v>
       </c>
-      <c r="H89" s="144" t="s">
+      <c r="H89" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I89" s="79"/>
@@ -29912,7 +29893,7 @@
       <c r="BM89" s="94"/>
       <c r="BN89" s="94"/>
     </row>
-    <row r="90" spans="2:66" ht="19.2" customHeight="1">
+    <row r="90" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B90" s="77" t="s">
         <v>228</v>
       </c>
@@ -29922,16 +29903,16 @@
       <c r="D90" s="78" t="s">
         <v>226</v>
       </c>
-      <c r="E90" s="142">
+      <c r="E90" s="115">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="F90" s="143">
+      <c r="F90" s="116">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G90" s="143">
+      <c r="G90" s="116">
         <v>-3.5000000000000003E-2</v>
       </c>
-      <c r="H90" s="144" t="s">
+      <c r="H90" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I90" s="79"/>
@@ -30046,7 +30027,7 @@
       <c r="BM90" s="94"/>
       <c r="BN90" s="94"/>
     </row>
-    <row r="91" spans="2:66" ht="19.2" customHeight="1">
+    <row r="91" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B91" s="77" t="s">
         <v>229</v>
       </c>
@@ -30056,16 +30037,16 @@
       <c r="D91" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="E91" s="142">
-        <v>0</v>
-      </c>
-      <c r="F91" s="143">
+      <c r="E91" s="115">
+        <v>0</v>
+      </c>
+      <c r="F91" s="116">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G91" s="143">
-        <v>0</v>
-      </c>
-      <c r="H91" s="144" t="s">
+      <c r="G91" s="116">
+        <v>0</v>
+      </c>
+      <c r="H91" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I91" s="79"/>
@@ -30180,7 +30161,7 @@
       <c r="BM91" s="94"/>
       <c r="BN91" s="94"/>
     </row>
-    <row r="92" spans="2:66" ht="19.2" customHeight="1">
+    <row r="92" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B92" s="77" t="s">
         <v>230</v>
       </c>
@@ -30190,16 +30171,16 @@
       <c r="D92" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="E92" s="142">
-        <v>0</v>
-      </c>
-      <c r="F92" s="143">
+      <c r="E92" s="115">
+        <v>0</v>
+      </c>
+      <c r="F92" s="116">
         <v>0.06</v>
       </c>
-      <c r="G92" s="143">
-        <v>0</v>
-      </c>
-      <c r="H92" s="144" t="s">
+      <c r="G92" s="116">
+        <v>0</v>
+      </c>
+      <c r="H92" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I92" s="79"/>
@@ -30314,7 +30295,7 @@
       <c r="BM92" s="94"/>
       <c r="BN92" s="94"/>
     </row>
-    <row r="93" spans="2:66" ht="19.2" customHeight="1">
+    <row r="93" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B93" s="77" t="s">
         <v>238</v>
       </c>
@@ -30324,16 +30305,16 @@
       <c r="D93" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E93" s="142">
+      <c r="E93" s="115">
         <v>0.8</v>
       </c>
-      <c r="F93" s="143">
+      <c r="F93" s="116">
         <v>0.02</v>
       </c>
-      <c r="G93" s="143">
+      <c r="G93" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H93" s="144" t="s">
+      <c r="H93" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I93" s="79"/>
@@ -30448,7 +30429,7 @@
       <c r="BM93" s="94"/>
       <c r="BN93" s="94"/>
     </row>
-    <row r="94" spans="2:66" ht="19.2" customHeight="1">
+    <row r="94" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B94" s="77" t="s">
         <v>238</v>
       </c>
@@ -30458,16 +30439,16 @@
       <c r="D94" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E94" s="142">
+      <c r="E94" s="115">
         <v>0.8</v>
       </c>
-      <c r="F94" s="143">
+      <c r="F94" s="116">
         <v>0.02</v>
       </c>
-      <c r="G94" s="143">
+      <c r="G94" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H94" s="144" t="s">
+      <c r="H94" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I94" s="79"/>
@@ -30582,7 +30563,7 @@
       <c r="BM94" s="94"/>
       <c r="BN94" s="94"/>
     </row>
-    <row r="95" spans="2:66" ht="19.2" customHeight="1">
+    <row r="95" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B95" s="77" t="s">
         <v>239</v>
       </c>
@@ -30592,16 +30573,16 @@
       <c r="D95" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="E95" s="142">
+      <c r="E95" s="115">
         <v>11.807</v>
       </c>
-      <c r="F95" s="143">
+      <c r="F95" s="116">
         <v>0.02</v>
       </c>
-      <c r="G95" s="143">
+      <c r="G95" s="116">
         <v>-0.02</v>
       </c>
-      <c r="H95" s="144" t="s">
+      <c r="H95" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I95" s="79"/>
@@ -30716,7 +30697,7 @@
       <c r="BM95" s="94"/>
       <c r="BN95" s="94"/>
     </row>
-    <row r="96" spans="2:66" ht="19.2" customHeight="1">
+    <row r="96" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B96" s="91" t="s">
         <v>243</v>
       </c>
@@ -30726,16 +30707,16 @@
       <c r="D96" s="78" t="s">
         <v>241</v>
       </c>
-      <c r="E96" s="142">
-        <v>0</v>
-      </c>
-      <c r="F96" s="143">
+      <c r="E96" s="115">
+        <v>0</v>
+      </c>
+      <c r="F96" s="116">
         <v>0.03</v>
       </c>
-      <c r="G96" s="143">
-        <v>0</v>
-      </c>
-      <c r="H96" s="144" t="s">
+      <c r="G96" s="116">
+        <v>0</v>
+      </c>
+      <c r="H96" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I96" s="79"/>
@@ -30850,7 +30831,7 @@
       <c r="BM96" s="94"/>
       <c r="BN96" s="94"/>
     </row>
-    <row r="97" spans="2:66" ht="19.2" customHeight="1">
+    <row r="97" spans="2:66" ht="19.149999999999999" customHeight="1">
       <c r="B97" s="90" t="s">
         <v>244</v>
       </c>
@@ -30860,16 +30841,16 @@
       <c r="D97" s="78" t="s">
         <v>241</v>
       </c>
-      <c r="E97" s="142">
-        <v>0</v>
-      </c>
-      <c r="F97" s="143">
+      <c r="E97" s="115">
+        <v>0</v>
+      </c>
+      <c r="F97" s="116">
         <v>0.03</v>
       </c>
-      <c r="G97" s="143">
-        <v>0</v>
-      </c>
-      <c r="H97" s="144" t="s">
+      <c r="G97" s="116">
+        <v>0</v>
+      </c>
+      <c r="H97" s="117" t="s">
         <v>46</v>
       </c>
       <c r="I97" s="97"/>
